--- a/bo_du_lieu_mau_doi_soat/4-ket-qua-dung-san/1-doi-soat-chuyen-khoan.xlsx
+++ b/bo_du_lieu_mau_doi_soat/4-ket-qua-dung-san/1-doi-soat-chuyen-khoan.xlsx
@@ -21,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot;đ&quot;"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,18 +33,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1B1F24"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1B1F24"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1B1F24"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF1B1F24"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -71,11 +116,41 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF111827"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F4E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEAE2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8E1E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -83,23 +158,140 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thick">
+        <color rgb="FF2A78D6"/>
+      </top>
+    </border>
+    <border>
+      <top style="thick">
+        <color rgb="FFD03B3B"/>
+      </top>
+    </border>
+    <border>
+      <top style="thick">
+        <color rgb="FF0CA30C"/>
+      </top>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -174,6 +366,268 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Giá trị đơn theo trạng thái</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Tóm tắt'!D11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="0CA30C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="EC835A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="D03B3B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="FAB219"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'Tóm tắt'!$B$12:$B$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tóm tắt'!$D$12:$D$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Tiền về theo giờ (theo ảnh đã ghép)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Tóm tắt'!C19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Tóm tắt'!$B$20:$B$26</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tóm tắt'!$C$20:$C$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4500000" cy="2232000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4500000" cy="2232000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -462,132 +916,613 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002A78D6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="2" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Đối soát chuyển khoản · 12/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>16 đơn · 17 ảnh · phải thu 20.200.000đ · đã nhận theo ảnh 16.970.000đ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ĐỐI SOÁT CHUYỂN KHOẢN · 12/10/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>16 đơn · 17 ảnh · tạo lúc 20:59 12/10/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+      <c r="M3" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ĐÃ THU THEO ẢNH</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>CÒN PHẢI THU</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>ĐƠN SẴN SÀNG GIAO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="10" t="n">
+        <v>16970000</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1"/>
+    <row r="8">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>84% của 20.200.000đ phải thu</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>6 đơn chưa xong</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>trên 16 đơn</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>THEO TRẠNG THÁI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Số đơn</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Giá trị đơn</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Đã nhận</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Còn thiếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="C12" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>DH1001 Nguyễn Văn An; DH1003 Lê Minh Châu; DH1005 Hoàng Thu Hà; DH1007 Đỗ Gia Huy; DH1008 Công ty TNHH Nội thất Gỗ Việt; DH1010 Đặng Hữu Phước; DH1012 Công ty CP Sự kiện Ánh Dương; DH1013 Trịnh Văn Long; DH1014 Trịnh Văn Long; DH1015 Lý Thanh Tâm</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="D12" s="19" t="n">
+        <v>15470000</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>15470000</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Trả thiếu</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="C13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>DH1002 Trần Thị Bình (thiếu 500.000đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="D13" s="19" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Chưa trả</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="C14" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>DH1004 Phạm Quốc Dũng (890.000đ); DH1016 Mai Phương Thảo (990.000đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="D14" s="19" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>1880000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Cần kiểm tra</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="C15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>DH1006 Võ Thanh Em; DH1009 Bùi Ngọc Lan; DH1011 Ngô Thị Kim</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ảnh</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>17</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Đã ghép 12 · Trùng 1 · Cần xem 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Lưu ý: số tiền lấy từ ảnh khách gửi. Đơn giá trị lớn cần xem sao kê ngân hàng trước khi giao. Agent không gửi tin nhắn; cột tin nhắn chỉ là bản soạn sẵn.</t>
+      <c r="D15" s="19" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>870000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>TIỀN VỀ THEO GIỜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Giờ</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Số tiền</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Giao dịch</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>1020000</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>7700000</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>350000</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>4790000</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>2360000</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>VIỆC CẦN LÀM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Mã đơn</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>SĐT</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>Còn thiếu</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>Việc cần làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Trả thiếu</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>DH1002</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>Trần Thị Bình</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>0902222333</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>Nhắc khách chuyển thêm 500.000đ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Chưa trả</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>DH1004</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Phạm Quốc Dũng</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>0904444555</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>890000</v>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Chưa trả</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>DH1016</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>Mai Phương Thảo</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>0918000111</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>990000</v>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Cần kiểm tra</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>DH1006</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Võ Thanh Em</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>0906666777</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>Mở ảnh z6042817840331_e0d5b8.jpg (chỉ đúng số tiền, chưa đủ để ghép) để xác nhận</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Cần kiểm tra</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>DH1009</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>Bùi Ngọc Lan</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>0909999000</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>Nhận dư 20.000đ; xác minh hoàn tiền hoặc trừ đơn sau</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Cần kiểm tra</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>DH1011</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>Ngô Thị Kim</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>0913444555</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>620000</v>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>Mở ảnh z6042818350288_6ac2e5.jpg (có mã đơn nhưng không đọc được số tiền) để xác nhận</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Ảnh: 17 · ghép tự động 12 (75%) · trùng 1 · cần xem 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>Hóa đơn điện tử: 8 số · khớp 2 · lệch 3 · tải trùng 1 · chỉ có ở một bên 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>Số tiền lấy từ ảnh khách gửi, chưa phải xác nhận tiền đã vào tài khoản. Xem sao kê trước khi giao đơn lớn. Agent không gửi tin nhắn.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="J6:L7"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="F6:H7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -614,791 +1549,791 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Mã đơn</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Số điện thoại</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>Phải thu</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>Đã nhận theo ảnh</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>Còn thiếu</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>Ảnh đã ghép</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>Căn cứ ghép</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>Việc cần làm</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="26" t="inlineStr">
         <is>
           <t>Tin nhắn nhắc (soạn sẵn, chưa gửi)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>DH1001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>Nguyễn Văn An</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>0901111222</t>
         </is>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="28" t="n">
         <v>450000</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="28" t="n">
         <v>450000</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="29" t="inlineStr">
         <is>
           <t>z6042817353390_8f1c2a.jpg</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="29" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Xác nhận đơn</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="J2" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
+        </is>
+      </c>
+      <c r="K2" s="29" t="inlineStr"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>DH1002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Trần Thị Bình</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>0902222333</t>
         </is>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="31" t="n">
         <v>1200000</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="31" t="n">
         <v>700000</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="31" t="n">
         <v>500000</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>Trả thiếu</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="32" t="inlineStr">
         <is>
           <t>z6042817411205_a7d3e9.jpg</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="32" t="inlineStr">
         <is>
           <t>có mã đơn</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="32" t="inlineStr">
         <is>
           <t>Nhắc khách chuyển thêm 500.000đ</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="32" t="inlineStr">
         <is>
           <t>Chào Trần Thị Bình, shop đã nhận 700.000đ cho đơn DH1002. Đơn còn thiếu 500.000đ, anh/chị kiểm tra giúp shop nhé. Cảm ơn anh/chị!</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>DH1003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>Lê Minh Châu</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>0912345678</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="28" t="n">
         <v>320000</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="28" t="n">
         <v>320000</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="29" t="inlineStr">
         <is>
           <t>z6042817502117_3b9e01.jpg</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="29" t="inlineStr">
         <is>
           <t>có số điện thoại, đúng số tiền</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Xác nhận đơn</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="J4" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>DH1004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Phạm Quốc Dũng</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>0904444555</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="34" t="n">
         <v>890000</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="34" t="n">
         <v>890000</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>Chưa trả</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Nhắc khách thanh toán</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Chào Phạm Quốc Dũng, đơn DH1004 (890.000đ) shop chưa thấy thanh toán. Nếu anh/chị đã chuyển, gửi giúp shop ảnh chuyển khoản nhé. Cảm ơn anh/chị!</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="H5" s="35" t="inlineStr"/>
+      <c r="I5" s="35" t="inlineStr"/>
+      <c r="J5" s="35" t="inlineStr">
+        <is>
+          <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
+        </is>
+      </c>
+      <c r="K5" s="35" t="inlineStr">
+        <is>
+          <t>Chào Phạm Quốc Dũng, với đơn DH1004 (890.000đ), shop chưa ghép được ảnh thanh toán trong dữ liệu cuối ngày. Nếu anh/chị đã chuyển, gửi giúp shop ảnh chuyển khoản nhé. Cảm ơn anh/chị!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>DH1005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Hoàng Thu Hà</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>0905555666</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="28" t="n">
         <v>560000</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="28" t="n">
         <v>560000</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>z6042817618842_c41f77.jpg, z6042817733015_77ab02.jpg</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Xác nhận đơn</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="J6" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
+        </is>
+      </c>
+      <c r="K6" s="29" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>DH1006</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Võ Thanh Em</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>0906666777</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="37" t="n">
         <v>250000</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="37" t="n">
         <v>250000</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>Cần kiểm tra</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="H7" s="38" t="inlineStr"/>
+      <c r="I7" s="38" t="inlineStr"/>
+      <c r="J7" s="38" t="inlineStr">
         <is>
           <t>Mở ảnh z6042817840331_e0d5b8.jpg (chỉ đúng số tiền, chưa đủ để ghép) để xác nhận</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="K7" s="38" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>DH1007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Đỗ Gia Huy</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>0907777888</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="28" t="n">
         <v>1500000</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="28" t="n">
         <v>1500000</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="29" t="inlineStr">
         <is>
           <t>z6042817921456_19ce4d.jpg</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Xác nhận đơn</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="J8" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
+        </is>
+      </c>
+      <c r="K8" s="29" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>DH1008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Công ty TNHH Nội thất Gỗ Việt</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>0243888999</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="28" t="n">
         <v>5400000</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="28" t="n">
         <v>5400000</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>z6042818034470_5d2a90.png</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Đủ theo ảnh; đơn lớn, xem sao kê trước khi giao</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="J9" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; xem sao kê trước khi xác nhận đơn hoặc giao hàng</t>
+        </is>
+      </c>
+      <c r="K9" s="29" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>DH1009</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Bùi Ngọc Lan</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>0909999000</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="37" t="n">
         <v>780000</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="37" t="n">
         <v>800000</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="36" t="inlineStr">
         <is>
           <t>Cần kiểm tra</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="38" t="inlineStr">
         <is>
           <t>z6042818115902_b8e6c3.jpg</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="38" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" s="38" t="inlineStr">
         <is>
           <t>Nhận dư 20.000đ; xác minh hoàn tiền hoặc trừ đơn sau</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="K10" s="38" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>DH1010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Đặng Hữu Phước</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>0911222333</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="28" t="n">
         <v>350000</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="28" t="n">
         <v>350000</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="29" t="inlineStr">
         <is>
           <t>z6042818207719_0f4ad1.jpg</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Xác nhận đơn</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="J11" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
+        </is>
+      </c>
+      <c r="K11" s="29" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>DH1011</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Ngô Thị Kim</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>0913444555</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="37" t="n">
         <v>620000</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="37" t="n">
         <v>620000</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="36" t="inlineStr">
         <is>
           <t>Cần kiểm tra</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="H12" s="38" t="inlineStr"/>
+      <c r="I12" s="38" t="inlineStr"/>
+      <c r="J12" s="38" t="inlineStr">
         <is>
           <t>Mở ảnh z6042818350288_6ac2e5.jpg (có mã đơn nhưng không đọc được số tiền) để xác nhận</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="K12" s="38" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>DH1012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Công ty CP Sự kiện Ánh Dương</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>0283777666</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="28" t="n">
         <v>3240000</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="28" t="n">
         <v>3240000</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="29" t="inlineStr">
         <is>
           <t>z6042818462531_2e7b9f.png</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Đủ theo ảnh; đơn lớn, xem sao kê trước khi giao</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="J13" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; xem sao kê trước khi xác nhận đơn hoặc giao hàng</t>
+        </is>
+      </c>
+      <c r="K13" s="29" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>DH1013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>Trịnh Văn Long</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>0915666777</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="28" t="n">
         <v>1150000</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="28" t="n">
         <v>1150000</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>z6042818573004_d9f310.jpg</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="29" t="inlineStr">
         <is>
           <t>1 lần chuyển cho 2 đơn: có mã các đơn, tổng tiền khớp</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Xác nhận đơn</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="J14" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
+        </is>
+      </c>
+      <c r="K14" s="29" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>DH1014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Trịnh Văn Long</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>0915666777</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="28" t="n">
         <v>400000</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="28" t="n">
         <v>400000</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="29" t="inlineStr">
         <is>
           <t>z6042818573004_d9f310.jpg</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>1 lần chuyển cho 2 đơn: có mã các đơn, tổng tiền khớp</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Xác nhận đơn</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="J15" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
+        </is>
+      </c>
+      <c r="K15" s="29" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>DH1015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Lý Thanh Tâm</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>0917888999</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="28" t="n">
         <v>2100000</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="28" t="n">
         <v>2100000</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="29" t="inlineStr">
         <is>
           <t>z6042818680147_41b8ac.jpg</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Đủ theo ảnh; đơn lớn, xem sao kê trước khi giao</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="J16" s="29" t="inlineStr">
+        <is>
+          <t>Đủ theo ảnh; xem sao kê trước khi xác nhận đơn hoặc giao hàng</t>
+        </is>
+      </c>
+      <c r="K16" s="29" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>DH1016</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Mai Phương Thảo</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>0918000111</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="34" t="n">
         <v>990000</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="34" t="n">
         <v>990000</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="33" t="inlineStr">
         <is>
           <t>Chưa trả</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Nhắc khách thanh toán</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Chào Mai Phương Thảo, đơn DH1016 (990.000đ) shop chưa thấy thanh toán. Nếu anh/chị đã chuyển, gửi giúp shop ảnh chuyển khoản nhé. Cảm ơn anh/chị!</t>
+      <c r="H17" s="35" t="inlineStr"/>
+      <c r="I17" s="35" t="inlineStr"/>
+      <c r="J17" s="35" t="inlineStr">
+        <is>
+          <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
+        </is>
+      </c>
+      <c r="K17" s="35" t="inlineStr">
+        <is>
+          <t>Chào Mai Phương Thảo, với đơn DH1016 (990.000đ), shop chưa ghép được ảnh thanh toán trong dữ liệu cuối ngày. Nếu anh/chị đã chuyển, gửi giúp shop ảnh chuyển khoản nhé. Cảm ơn anh/chị!</t>
         </is>
       </c>
     </row>
@@ -1430,102 +2365,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Tệp ảnh</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>Số tiền đọc được</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Nội dung</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>Người chuyển</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>Mã giao dịch</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>Thời gian</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>Ghép vào đơn</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>Căn cứ</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>Kết quả</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>Chữ đọc được trên ảnh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>z6042817353390_8f1c2a.jpg</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="40" t="n">
         <v>450000</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>DH1001 NGUYEN VAN AN</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="39" t="inlineStr">
         <is>
           <t>NGUYEN VAN AN</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="39" t="inlineStr">
         <is>
           <t>FT26285104411</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="39" t="inlineStr">
         <is>
           <t>12/10/2026 08:41:07</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="39" t="inlineStr">
         <is>
           <t>DH1001</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="39" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="39" t="inlineStr">
         <is>
           <t>08:41 al RKM
 Sen Vàng Bank
@@ -1542,46 +2477,46 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>z6042817411205_a7d3e9.jpg</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="40" t="n">
         <v>700000</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>DH1002 chuyen truoc</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="39" t="n"/>
+      <c r="E3" s="39" t="inlineStr">
         <is>
           <t>FT26285219034</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="39" t="inlineStr">
         <is>
           <t>12/10/2026 09:12:45</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="39" t="inlineStr">
         <is>
           <t>DH1002</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="39" t="inlineStr">
         <is>
           <t>có mã đơn</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="39" t="inlineStr">
         <is>
           <t>09:12 | o_o
 Bién Xanh Bank
@@ -1599,46 +2534,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>z6042817502117_3b9e01.jpg</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="40" t="n">
         <v>320000</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>0912345678 thanh toan</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="39" t="n"/>
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>MM2610120933</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>09:33 - 12/10/2026</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="39" t="inlineStr">
         <is>
           <t>DH1003</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="39" t="inlineStr">
         <is>
           <t>có số điện thoại, đúng số tiền</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="39" t="inlineStr">
         <is>
           <t>09:33
 "' ï
@@ -1659,50 +2594,50 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>z6042817618842_c41f77.jpg</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="40" t="n">
         <v>300000</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>DH1005 lan 1</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="39" t="inlineStr">
         <is>
           <t>HOANG THU HA</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="39" t="inlineStr">
         <is>
           <t>DT26101200871</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="39" t="inlineStr">
         <is>
           <t>12/10/2026 10:02:19</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="39" t="inlineStr">
         <is>
           <t>DH1005</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="39" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="39" t="inlineStr">
         <is>
           <t>10:02
 aul
@@ -1722,50 +2657,50 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>z6042817733015_77ab02.jpg</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="40" t="n">
         <v>260000</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>DH1005 lan 2</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>HOANG THU HA</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>FT26285310927</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="39" t="inlineStr">
         <is>
           <t>12/10/2026 15:47:52</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="39" t="inlineStr">
         <is>
           <t>DH1005</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="39" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="39" t="inlineStr">
         <is>
           <t>15:47 a l
 Sen Vàng Bank
@@ -1782,46 +2717,46 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>z6042817840331_e0d5b8.jpg</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="42" t="n">
         <v>250000</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>chuyen tien</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>FT26285322108</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>12/10/2026 10:50:31</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="41" t="inlineStr">
         <is>
           <t>DH1006</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="41" t="inlineStr">
         <is>
           <t>Chỉ đúng số tiền, chưa đủ để ghép</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="41" t="inlineStr">
         <is>
           <t>Gợi ý, cần người xác nhận</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="41" t="inlineStr">
         <is>
           <t>40:50 "Am l
 Biên Xanh Bank
@@ -1839,50 +2774,50 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>z6042817921456_19ce4d.jpg</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="40" t="n">
         <v>1500000</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>DO GIA HUY thanh toan</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>DO GIA HUY</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>DT26101201544</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="39" t="inlineStr">
         <is>
           <t>12/10/2026 11:05:44</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="39" t="inlineStr">
         <is>
           <t>DH1007</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="39" t="inlineStr">
         <is>
           <t>có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="39" t="inlineStr">
         <is>
           <t>11:05
 aul
@@ -1902,38 +2837,42 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>z6042818034470_5d2a90.png</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="40" t="n">
         <v>5400000</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>DH1008 TT HD 00000126</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="inlineStr">
+        <is>
+          <t>12/10/2026 11:31:02</t>
+        </is>
+      </c>
+      <c r="G9" s="39" t="inlineStr">
         <is>
           <t>DH1008</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="39" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="39" t="inlineStr">
         <is>
           <t>Kết quả giao dịch: Chuyên khoản thành công
 1903 2222 1111
@@ -1957,38 +2896,38 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>z6042818115902_b8e6c3.jpg</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="40" t="n">
         <v>800000</v>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="C10" s="39" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="inlineStr">
         <is>
           <t>11:42 - 12/10/2026</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="39" t="inlineStr">
         <is>
           <t>DH1009</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="39" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="39" t="inlineStr">
         <is>
           <t>11:42
 "' ï
@@ -2009,46 +2948,46 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>z6042818207719_0f4ad1.jpg</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="40" t="n">
         <v>350000</v>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="39" t="inlineStr">
         <is>
           <t>DANG HUU PHUOC</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="39" t="inlineStr">
         <is>
           <t>FT26285512870</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="39" t="inlineStr">
         <is>
           <t>42/10/2026 13:22:16</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="39" t="inlineStr">
         <is>
           <t>DH1010</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="39" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="39" t="inlineStr">
         <is>
           <t>13:22 wt a)
 Sen Vang Bank
@@ -2065,48 +3004,48 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>z6042818350288_6ac2e5.jpg</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="43" t="inlineStr">
         <is>
           <t>DH1011 Ngo Thi Kim</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>NGO THI KIM</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="43" t="inlineStr">
         <is>
           <t>DT26101202230</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="43" t="inlineStr">
         <is>
           <t>12/10/2026 14:01:33</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="43" t="inlineStr">
         <is>
           <t>DH1011</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="43" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="43" t="inlineStr">
         <is>
           <t>Không đọc được số tiền; mở ảnh kiểm tra</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="43" t="inlineStr">
         <is>
           <t>Người chuyển: NGO THI KIM
 Từ tài khoản: 2201 8899 7766
@@ -2120,42 +3059,46 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>z6042818462531_2e7b9f.png</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="40" t="n">
         <v>3240000</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
         <is>
           <t>DH1012 thanh toan hoa don 00000127</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="inlineStr">
         <is>
           <t>FT26285618833</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="F13" s="39" t="inlineStr">
+        <is>
+          <t>12/40/2026 14:20:09</t>
+        </is>
+      </c>
+      <c r="G13" s="39" t="inlineStr">
         <is>
           <t>DH1012</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="39" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="39" t="inlineStr">
         <is>
           <t>Kết quả giao dịch: Chuyên khoản thành công
 1903 2222 1111
@@ -2179,46 +3122,46 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>z6042818573004_d9f310.jpg</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="40" t="n">
         <v>1550000</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>DH1013 DH1014</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>FT26285702264</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>12/10/2026 14:48:55</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="39" t="inlineStr">
         <is>
           <t>DH1013, DH1014</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="39" t="inlineStr">
         <is>
           <t>1 lần chuyển cho 2 đơn: có mã các đơn, tổng tiền khớp</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="39" t="inlineStr">
         <is>
           <t>Đã ghép, chia cho 2 đơn</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="39" t="inlineStr">
         <is>
           <t>14:48 || o_o
 Bién Xanh Bank
@@ -2236,46 +3179,46 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>z6042818680147_41b8ac.jpg</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="40" t="n">
         <v>2100000</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="39" t="inlineStr">
         <is>
           <t>DH1015 Ly Thanh Tam</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="inlineStr">
         <is>
           <t>MM2610121537</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="39" t="inlineStr">
         <is>
           <t>15:37 - 12/10/2026</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="39" t="inlineStr">
         <is>
           <t>DH1015</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="39" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="39" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="39" t="inlineStr">
         <is>
           <t>15:37
 "' ï
@@ -2296,46 +3239,46 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>z6042818791260_a3c6d2.jpg</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="42" t="n">
         <v>430000</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>DH0987 Phan Van Quang</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="41" t="inlineStr">
         <is>
           <t>PHAN VAN QUANG</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="41" t="inlineStr">
         <is>
           <t>FT26285800412</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="41" t="inlineStr">
         <is>
           <t>12/10/2026 16:12:40</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="G16" s="41" t="n"/>
+      <c r="H16" s="41" t="inlineStr">
         <is>
           <t>Không thấy mã đơn, SĐT, tên khách hay số tiền nào khớp</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="41" t="inlineStr">
         <is>
           <t>Chưa ghép được; xem ảnh và tìm đơn</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J16" s="41" t="inlineStr">
         <is>
           <t>46:12 | MHỊ
 Sen Vàng Bank
@@ -2352,42 +3295,42 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>z6042819002388_3b9e01.jpg</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="44" t="n">
         <v>320000</v>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="43" t="inlineStr">
         <is>
           <t>0912345678 thanh toan</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D17" s="43" t="n"/>
+      <c r="E17" s="43" t="inlineStr">
         <is>
           <t>MM2610120933</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="43" t="inlineStr">
         <is>
           <t>09:33 - 12/10/2026</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G17" s="43" t="n"/>
+      <c r="H17" s="43" t="inlineStr">
         <is>
           <t>có số điện thoại, đúng số tiền</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="43" t="inlineStr">
         <is>
           <t>Trùng với ảnh z6042817502117_3b9e01.jpg; không cộng tiền</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="43" t="inlineStr">
         <is>
           <t>09:33
 "' ï
@@ -2408,28 +3351,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>z6042819115630_7e21aa.jpg</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="43" t="n"/>
+      <c r="D18" s="43" t="n"/>
+      <c r="E18" s="43" t="n"/>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="43" t="n"/>
+      <c r="H18" s="43" t="inlineStr">
         <is>
           <t>Không thấy mã đơn, SĐT, tên khách hay số tiền nào khớp</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="43" t="inlineStr">
         <is>
           <t>Không đọc được số tiền; có thể không phải biên nhận</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="43" t="inlineStr">
         <is>
           <t>Mau bó hoa số 3 —- còn hàng không shop?</t>
         </is>

--- a/bo_du_lieu_mau_doi_soat/4-ket-qua-dung-san/1-doi-soat-chuyen-khoan.xlsx
+++ b/bo_du_lieu_mau_doi_soat/4-ket-qua-dung-san/1-doi-soat-chuyen-khoan.xlsx
@@ -976,7 +976,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>16 đơn · 17 ảnh · tạo lúc 20:59 12/10/2026</t>
+          <t>16 đơn · 17 ảnh · tạo lúc 21:39 12/10/2026</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>

--- a/bo_du_lieu_mau_doi_soat/4-ket-qua-dung-san/1-doi-soat-chuyen-khoan.xlsx
+++ b/bo_du_lieu_mau_doi_soat/4-ket-qua-dung-san/1-doi-soat-chuyen-khoan.xlsx
@@ -976,7 +976,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>16 đơn · 17 ảnh · tạo lúc 21:39 12/10/2026</t>
+          <t>16 đơn · 17 ảnh · tạo lúc 21:43 12/10/2026</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>

--- a/bo_du_lieu_mau_doi_soat/4-ket-qua-dung-san/1-doi-soat-chuyen-khoan.xlsx
+++ b/bo_du_lieu_mau_doi_soat/4-ket-qua-dung-san/1-doi-soat-chuyen-khoan.xlsx
@@ -10,8 +10,10 @@
     <sheet name="Tóm tắt" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Đơn hàng" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Ảnh chuyển khoản" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="_bieu_do" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tóm tắt'!$A$1:$Q$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đơn hàng'!$A$1:$K$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ảnh chuyển khoản'!$A$1:$J$18</definedName>
   </definedNames>
@@ -21,10 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0&quot;đ&quot;"/>
+    <numFmt numFmtId="165" formatCode="0&quot; đơn&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,59 +38,182 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0D0F12"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1F2A06"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF5B6170"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0D0F12"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0D0F12"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF9CA3AF"/>
+      <color rgb="FF5B6170"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF0D0F12"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0D0F12"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF16A34A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF9097A3"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFE5484D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF5B6170"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0D0F12"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF5B6170"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1F2A06"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0D0F12"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF5B6170"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFE5484D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFC48A00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0D0F12"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0CA30C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF9097A3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0D0F12"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF6B7280"/>
+      <color rgb="FFEC835A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFD03B3B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFAB219"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFEC835A"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF1B1F24"/>
-      <sz val="24"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF6B7280"/>
+      <color rgb="FFD03B3B"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF1B1F24"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF1B1F24"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF1B1F24"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF6B7280"/>
-      <sz val="10"/>
+      <color rgb="FFFAB219"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -116,17 +242,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF111827"/>
+        <fgColor rgb="FFEEF1F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9FAFB"/>
+        <fgColor rgb="FFC8F26D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F4E3"/>
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F6F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -150,7 +281,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -158,98 +289,139 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <top style="thick">
-        <color rgb="FF2A78D6"/>
-      </top>
-    </border>
-    <border>
-      <top style="thick">
-        <color rgb="FFD03B3B"/>
-      </top>
-    </border>
-    <border>
-      <top style="thick">
-        <color rgb="FF0CA30C"/>
-      </top>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FFE5E7EB"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="24" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -372,21 +544,173 @@
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Giá trị đơn theo trạng thái</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'_bieu_do'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:pattFill prst="wdUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="D9DCE2"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="F1F2F5"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="E1E3E8"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="F4772E"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="F4772E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'_bieu_do'!$A$2:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'_bieu_do'!$B$2:$B$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="45"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'_bieu_do'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="32000">
+              <a:solidFill>
+                <a:srgbClr val="9B87F5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'_bieu_do'!$A$2:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'_bieu_do'!$C$2:$C$12</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
     <plotArea>
       <barChart>
         <barDir val="bar"/>
@@ -396,7 +720,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Tóm tắt'!D11</f>
+              <f>'_bieu_do'!B13</f>
             </strRef>
           </tx>
           <spPr>
@@ -454,100 +778,16 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Tóm tắt'!$B$12:$B$15</f>
+              <f>'_bieu_do'!$A$14:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tóm tắt'!$D$12:$D$15</f>
+              <f>'_bieu_do'!$B$14:$B$17</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="60"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Tiền về theo giờ (theo ảnh đã ghép)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Tóm tắt'!C19</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Tóm tắt'!$B$20:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Tóm tắt'!$C$20:$C$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="80"/>
+        <gapWidth val="55"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -585,12 +825,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4500000" cy="2232000"/>
+    <ext cx="7740000" cy="2592000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -607,12 +847,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4500000" cy="2232000"/>
+    <ext cx="4896000" cy="2015999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -622,6 +862,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4896000" cy="1512000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -916,26 +1178,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002A78D6"/>
+    <tabColor rgb="00C8F26D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="2" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="12.5" customWidth="1" min="2" max="2"/>
+    <col width="12.5" customWidth="1" min="3" max="3"/>
+    <col width="12.5" customWidth="1" min="4" max="4"/>
+    <col width="2.5" customWidth="1" min="5" max="5"/>
+    <col width="12.5" customWidth="1" min="6" max="6"/>
+    <col width="12.5" customWidth="1" min="7" max="7"/>
+    <col width="12.5" customWidth="1" min="8" max="8"/>
+    <col width="2.5" customWidth="1" min="9" max="9"/>
+    <col width="12.5" customWidth="1" min="10" max="10"/>
+    <col width="12.5" customWidth="1" min="11" max="11"/>
+    <col width="12.5" customWidth="1" min="12" max="12"/>
+    <col width="2.5" customWidth="1" min="13" max="13"/>
+    <col width="12.5" customWidth="1" min="14" max="14"/>
+    <col width="12.5" customWidth="1" min="15" max="15"/>
+    <col width="12.5" customWidth="1" min="16" max="16"/>
+    <col width="3" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -952,33 +1218,55 @@
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ĐỐI SOÁT CHUYỂN KHOẢN · 12/10/2026</t>
+          <t>▤  Đối soát</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Tổng quan</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Việc cần làm</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Đơn hàng</t>
+        </is>
+      </c>
       <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="n"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Báo cáo cuối ngày · 12/10/2026</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>16 đơn · 17 ảnh · tạo lúc 21:43 12/10/2026</t>
-        </is>
-      </c>
+      <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
       <c r="D3" s="1" t="n"/>
       <c r="E3" s="1" t="n"/>
@@ -990,535 +1278,1788 @@
       <c r="K3" s="1" t="n"/>
       <c r="L3" s="1" t="n"/>
       <c r="M3" s="1" t="n"/>
+      <c r="N3" s="1" t="n"/>
+      <c r="O3" s="1" t="n"/>
+      <c r="P3" s="1" t="n"/>
+      <c r="Q3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Đối soát cuối ngày 👋</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="1" t="n"/>
+      <c r="I4" s="1" t="n"/>
+      <c r="J4" s="1" t="n"/>
+      <c r="K4" s="1" t="n"/>
+      <c r="L4" s="1" t="n"/>
+      <c r="M4" s="1" t="n"/>
+      <c r="N4" s="1" t="n"/>
+      <c r="O4" s="1" t="n"/>
+      <c r="P4" s="1" t="n"/>
+      <c r="Q4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ĐÃ THU THEO ẢNH</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>CÒN PHẢI THU</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>ĐƠN SẴN SÀNG GIAO</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="10" t="n">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>16 đơn · 17 ảnh chuyển khoản · 12/10/2026 · Hôm nay thu được bao nhiêu, còn ai chưa trả, đơn nào giao được.</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
+      <c r="I5" s="1" t="n"/>
+      <c r="J5" s="1" t="n"/>
+      <c r="K5" s="1" t="n"/>
+      <c r="L5" s="1" t="n"/>
+      <c r="M5" s="1" t="n"/>
+      <c r="N5" s="1" t="n"/>
+      <c r="O5" s="1" t="n"/>
+      <c r="P5" s="1" t="n"/>
+      <c r="Q5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="n"/>
+      <c r="M6" s="1" t="n"/>
+      <c r="N6" s="1" t="n"/>
+      <c r="O6" s="1" t="n"/>
+      <c r="P6" s="1" t="n"/>
+      <c r="Q6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Tổng giá trị đơn</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>◫</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Còn phải thu</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Đơn sẵn sàng giao</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>⛟</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n"/>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Khách cần nhắc</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>☏</t>
+        </is>
+      </c>
+      <c r="Q7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="11" t="n">
+        <v>20200000</v>
+      </c>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="11" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="I8" s="1" t="n"/>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>10/16</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n"/>
+      <c r="N8" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="E9" s="1" t="n"/>
+      <c r="I9" s="1" t="n"/>
+      <c r="M9" s="1" t="n"/>
+      <c r="Q9" s="1" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>▲ 16 đơn hôm nay</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>▼ 6 đơn chưa xong</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="1" t="n"/>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>▲ 15.470.000đ đủ tiền</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="1" t="n"/>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>▼ 2.380.000đ cần đòi</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="1" t="n"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Xem chi tiết ↗</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Xem chi tiết ↗</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>Xem chi tiết ↗</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="15" t="inlineStr">
+        <is>
+          <t>Xem chi tiết ↗</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
+      <c r="M12" s="1" t="n"/>
+      <c r="N12" s="1" t="n"/>
+      <c r="O12" s="1" t="n"/>
+      <c r="P12" s="1" t="n"/>
+      <c r="Q12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>⚠  Số tiền lấy từ ảnh khách gửi, chưa phải xác nhận tiền đã vào tài khoản. Xem sao kê trước khi giao đơn lớn. Agent không tự gửi tin nhắn.</t>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="1" t="n"/>
+      <c r="E14" s="1" t="n"/>
+      <c r="F14" s="1" t="n"/>
+      <c r="G14" s="1" t="n"/>
+      <c r="H14" s="1" t="n"/>
+      <c r="I14" s="1" t="n"/>
+      <c r="J14" s="1" t="n"/>
+      <c r="K14" s="1" t="n"/>
+      <c r="L14" s="1" t="n"/>
+      <c r="M14" s="1" t="n"/>
+      <c r="N14" s="1" t="n"/>
+      <c r="O14" s="1" t="n"/>
+      <c r="P14" s="1" t="n"/>
+      <c r="Q14" s="1" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Tổng quan thu tiền</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>···</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n"/>
+      <c r="N15" s="17" t="inlineStr">
+        <is>
+          <t>Ý chính hôm nay</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="18" t="inlineStr">
+        <is>
+          <t>···</t>
+        </is>
+      </c>
+      <c r="Q15" s="1" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="11" t="n">
         <v>16970000</v>
       </c>
-      <c r="F6" s="10" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="J6" s="11" t="n">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>84% ↗</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>Phải thu</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>Còn phải thu</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="1" t="n"/>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>Những điều cần biết trước khi chốt ngày</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="1" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>20.200.000đ</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>3.250.000đ</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="1" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="1" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>▨ Tiền về theo giờ    ● Giờ tiền về nhiều nhất</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="1" t="n"/>
+      <c r="N18" s="23" t="inlineStr">
+        <is>
+          <t>● Thu 84%</t>
+        </is>
+      </c>
+      <c r="Q18" s="1" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="1" t="n"/>
+      <c r="N19" s="24" t="inlineStr">
+        <is>
+          <t>16.970.000đ trên 20.200.000đ; 10 đơn đủ tiền có thể giao.</t>
+        </is>
+      </c>
+      <c r="Q19" s="1" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
+      <c r="L20" s="9" t="n"/>
+      <c r="M20" s="1" t="n"/>
+      <c r="Q20" s="1" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="1" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="9" t="n"/>
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="1" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="9" t="n"/>
+      <c r="M22" s="1" t="n"/>
+      <c r="N22" s="25" t="inlineStr">
+        <is>
+          <t>● 6 đơn chưa xong</t>
+        </is>
+      </c>
+      <c r="Q22" s="1" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="1" t="n"/>
+      <c r="N23" s="24" t="inlineStr">
+        <is>
+          <t>Còn 3.250.000đ: 1 thiếu, 2 chưa thấy ảnh, 3 cần mở ảnh.</t>
+        </is>
+      </c>
+      <c r="Q23" s="1" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="1" t="n"/>
+      <c r="Q24" s="1" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="1" t="n"/>
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="9" t="n"/>
+      <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="1" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="1" t="n"/>
+      <c r="N26" s="26" t="inlineStr">
+        <is>
+          <t>● 3 đơn lớn chờ sao kê</t>
+        </is>
+      </c>
+      <c r="Q26" s="1" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="1" t="n"/>
+      <c r="N27" s="24" t="inlineStr">
+        <is>
+          <t>Trị giá 10.740.000đ; xác nhận tiền về rồi mới giao.</t>
+        </is>
+      </c>
+      <c r="Q27" s="1" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="n"/>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" s="9" t="n"/>
+      <c r="M28" s="1" t="n"/>
+      <c r="Q28" s="1" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="1" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="1" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="9" t="n"/>
+      <c r="M30" s="1" t="n"/>
+      <c r="N30" s="25" t="inlineStr">
+        <is>
+          <t>● 6 hóa đơn cần xem</t>
+        </is>
+      </c>
+      <c r="Q30" s="1" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
+      <c r="L31" s="9" t="n"/>
+      <c r="M31" s="1" t="n"/>
+      <c r="N31" s="24" t="inlineStr">
+        <is>
+          <t>3 lệch, 1 trùng, 2 một bên; 2 khớp.</t>
+        </is>
+      </c>
+      <c r="Q31" s="1" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="n"/>
+      <c r="M32" s="1" t="n"/>
+      <c r="Q32" s="1" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="1" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="1" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="1" t="n"/>
+      <c r="D34" s="1" t="n"/>
+      <c r="E34" s="1" t="n"/>
+      <c r="F34" s="1" t="n"/>
+      <c r="G34" s="1" t="n"/>
+      <c r="H34" s="1" t="n"/>
+      <c r="I34" s="1" t="n"/>
+      <c r="J34" s="1" t="n"/>
+      <c r="K34" s="1" t="n"/>
+      <c r="L34" s="1" t="n"/>
+      <c r="M34" s="1" t="n"/>
+      <c r="N34" s="1" t="n"/>
+      <c r="O34" s="1" t="n"/>
+      <c r="P34" s="1" t="n"/>
+      <c r="Q34" s="1" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Giao dịch trong ngày</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>···</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="n"/>
+      <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>Giá trị đơn theo trạng thái</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="18" t="inlineStr">
+        <is>
+          <t>···</t>
+        </is>
+      </c>
+      <c r="Q35" s="1" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>12 giao dịch</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>Cao điểm 11h</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="1" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="9" t="n"/>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="9" t="n"/>
+      <c r="P36" s="9" t="n"/>
+      <c r="Q36" s="1" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="1" t="n"/>
+      <c r="J37" s="28" t="inlineStr">
+        <is>
+          <t>● Đã trả đủ</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="29" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" ht="22" customHeight="1"/>
-    <row r="8">
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>84% của 20.200.000đ phải thu</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>6 đơn chưa xong</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>trên 16 đơn</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>THEO TRẠNG THÁI</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="15" t="inlineStr">
+      <c r="O37" s="9" t="n"/>
+      <c r="P37" s="30" t="n">
+        <v>15470000</v>
+      </c>
+      <c r="Q37" s="1" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="1" t="n"/>
+      <c r="J38" s="31" t="inlineStr">
+        <is>
+          <t>● Trả thiếu</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="n"/>
+      <c r="L38" s="9" t="n"/>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="9" t="n"/>
+      <c r="P38" s="30" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="Q38" s="1" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="n"/>
+      <c r="I39" s="1" t="n"/>
+      <c r="J39" s="32" t="inlineStr">
+        <is>
+          <t>● Chưa trả</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="n"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" s="9" t="n"/>
+      <c r="P39" s="30" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="Q39" s="1" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="n"/>
+      <c r="I40" s="1" t="n"/>
+      <c r="J40" s="33" t="inlineStr">
+        <is>
+          <t>● Cần kiểm tra</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="n"/>
+      <c r="L40" s="9" t="n"/>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" s="9" t="n"/>
+      <c r="P40" s="30" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="Q40" s="1" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="1" t="n"/>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="9" t="n"/>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="9" t="n"/>
+      <c r="P41" s="9" t="n"/>
+      <c r="Q41" s="1" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
+      <c r="I42" s="1" t="n"/>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="9" t="n"/>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="9" t="n"/>
+      <c r="P42" s="9" t="n"/>
+      <c r="Q42" s="1" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="1" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="9" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="9" t="n"/>
+      <c r="P43" s="9" t="n"/>
+      <c r="Q43" s="1" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="1" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
+      <c r="L44" s="9" t="n"/>
+      <c r="M44" s="9" t="n"/>
+      <c r="N44" s="9" t="n"/>
+      <c r="O44" s="9" t="n"/>
+      <c r="P44" s="9" t="n"/>
+      <c r="Q44" s="1" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="1" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n"/>
+      <c r="P45" s="9" t="n"/>
+      <c r="Q45" s="1" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="1" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="9" t="n"/>
+      <c r="O46" s="9" t="n"/>
+      <c r="P46" s="9" t="n"/>
+      <c r="Q46" s="1" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="1" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="9" t="n"/>
+      <c r="O47" s="9" t="n"/>
+      <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="1" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
+      <c r="I48" s="1" t="n"/>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="9" t="n"/>
+      <c r="L48" s="9" t="n"/>
+      <c r="M48" s="9" t="n"/>
+      <c r="N48" s="9" t="n"/>
+      <c r="O48" s="9" t="n"/>
+      <c r="P48" s="9" t="n"/>
+      <c r="Q48" s="1" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
+      <c r="I49" s="1" t="n"/>
+      <c r="J49" s="9" t="n"/>
+      <c r="K49" s="9" t="n"/>
+      <c r="L49" s="9" t="n"/>
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="9" t="n"/>
+      <c r="O49" s="9" t="n"/>
+      <c r="P49" s="9" t="n"/>
+      <c r="Q49" s="1" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="1" t="n"/>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+      <c r="L50" s="9" t="n"/>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="9" t="n"/>
+      <c r="O50" s="9" t="n"/>
+      <c r="P50" s="9" t="n"/>
+      <c r="Q50" s="1" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="1" t="n"/>
+      <c r="C51" s="1" t="n"/>
+      <c r="D51" s="1" t="n"/>
+      <c r="E51" s="1" t="n"/>
+      <c r="F51" s="1" t="n"/>
+      <c r="G51" s="1" t="n"/>
+      <c r="H51" s="1" t="n"/>
+      <c r="I51" s="1" t="n"/>
+      <c r="J51" s="1" t="n"/>
+      <c r="K51" s="1" t="n"/>
+      <c r="L51" s="1" t="n"/>
+      <c r="M51" s="1" t="n"/>
+      <c r="N51" s="1" t="n"/>
+      <c r="O51" s="1" t="n"/>
+      <c r="P51" s="1" t="n"/>
+      <c r="Q51" s="1" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>Việc cần làm hôm nay</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n"/>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="9" t="n"/>
+      <c r="K52" s="9" t="n"/>
+      <c r="L52" s="9" t="n"/>
+      <c r="M52" s="9" t="n"/>
+      <c r="N52" s="9" t="n"/>
+      <c r="O52" s="9" t="n"/>
+      <c r="P52" s="18" t="inlineStr">
+        <is>
+          <t>···</t>
+        </is>
+      </c>
+      <c r="Q52" s="1" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n"/>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>Nhắc tiền còn thiếu trước, rồi đơn chưa thấy ảnh, rồi đơn cần mở ảnh</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="9" t="n"/>
+      <c r="I53" s="9" t="n"/>
+      <c r="J53" s="9" t="n"/>
+      <c r="K53" s="9" t="n"/>
+      <c r="L53" s="9" t="n"/>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="9" t="n"/>
+      <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="1" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n"/>
+      <c r="B54" s="20" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Số đơn</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>Giá trị đơn</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>Đã nhận</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>Mã đơn · SĐT</t>
+        </is>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>Việc cần làm</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
+      <c r="L54" s="9" t="n"/>
+      <c r="M54" s="9" t="n"/>
+      <c r="N54" s="15" t="inlineStr">
         <is>
           <t>Còn thiếu</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Đã trả đủ</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <v>15470000</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>15470000</v>
-      </c>
-      <c r="G12" s="19" t="n">
+      <c r="O54" s="9" t="n"/>
+      <c r="P54" s="9" t="n"/>
+      <c r="Q54" s="1" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="34" t="inlineStr">
+        <is>
+          <t>Trả thiếu</t>
+        </is>
+      </c>
+      <c r="C55" s="35" t="inlineStr">
+        <is>
+          <t>Trần Thị Bình</t>
+        </is>
+      </c>
+      <c r="D55" s="36" t="n"/>
+      <c r="E55" s="36" t="n"/>
+      <c r="F55" s="36" t="n"/>
+      <c r="G55" s="37" t="inlineStr">
+        <is>
+          <t>DH1002 · 0902222333</t>
+        </is>
+      </c>
+      <c r="H55" s="38" t="inlineStr">
+        <is>
+          <t>Nhắc khách chuyển thêm 500.000đ</t>
+        </is>
+      </c>
+      <c r="I55" s="36" t="n"/>
+      <c r="J55" s="36" t="n"/>
+      <c r="K55" s="36" t="n"/>
+      <c r="L55" s="36" t="n"/>
+      <c r="M55" s="36" t="n"/>
+      <c r="N55" s="36" t="n"/>
+      <c r="O55" s="36" t="n"/>
+      <c r="P55" s="39" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Q55" s="1" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="1" t="n"/>
+      <c r="B56" s="40" t="inlineStr">
+        <is>
+          <t>Chưa trả</t>
+        </is>
+      </c>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>Phạm Quốc Dũng</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="42" t="inlineStr">
+        <is>
+          <t>DH1004 · 0904444555</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="n"/>
+      <c r="J56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
+      <c r="L56" s="9" t="n"/>
+      <c r="M56" s="9" t="n"/>
+      <c r="N56" s="9" t="n"/>
+      <c r="O56" s="9" t="n"/>
+      <c r="P56" s="30" t="n">
+        <v>890000</v>
+      </c>
+      <c r="Q56" s="1" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="1" t="n"/>
+      <c r="B57" s="40" t="inlineStr">
+        <is>
+          <t>Chưa trả</t>
+        </is>
+      </c>
+      <c r="C57" s="35" t="inlineStr">
+        <is>
+          <t>Mai Phương Thảo</t>
+        </is>
+      </c>
+      <c r="D57" s="36" t="n"/>
+      <c r="E57" s="36" t="n"/>
+      <c r="F57" s="36" t="n"/>
+      <c r="G57" s="37" t="inlineStr">
+        <is>
+          <t>DH1016 · 0918000111</t>
+        </is>
+      </c>
+      <c r="H57" s="38" t="inlineStr">
+        <is>
+          <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
+        </is>
+      </c>
+      <c r="I57" s="36" t="n"/>
+      <c r="J57" s="36" t="n"/>
+      <c r="K57" s="36" t="n"/>
+      <c r="L57" s="36" t="n"/>
+      <c r="M57" s="36" t="n"/>
+      <c r="N57" s="36" t="n"/>
+      <c r="O57" s="36" t="n"/>
+      <c r="P57" s="39" t="n">
+        <v>990000</v>
+      </c>
+      <c r="Q57" s="1" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="1" t="n"/>
+      <c r="B58" s="43" t="inlineStr">
+        <is>
+          <t>Cần kiểm tra</t>
+        </is>
+      </c>
+      <c r="C58" s="41" t="inlineStr">
+        <is>
+          <t>Võ Thanh Em</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="42" t="inlineStr">
+        <is>
+          <t>DH1006 · 0906666777</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>Mở ảnh z6042817840331_e0d5b8.jpg (chỉ đúng số tiền, chưa đủ để ghép) để xác nhận</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
+      <c r="L58" s="9" t="n"/>
+      <c r="M58" s="9" t="n"/>
+      <c r="N58" s="9" t="n"/>
+      <c r="O58" s="9" t="n"/>
+      <c r="P58" s="30" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q58" s="1" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="1" t="n"/>
+      <c r="B59" s="43" t="inlineStr">
+        <is>
+          <t>Cần kiểm tra</t>
+        </is>
+      </c>
+      <c r="C59" s="35" t="inlineStr">
+        <is>
+          <t>Bùi Ngọc Lan</t>
+        </is>
+      </c>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="37" t="inlineStr">
+        <is>
+          <t>DH1009 · 0909999000</t>
+        </is>
+      </c>
+      <c r="H59" s="38" t="inlineStr">
+        <is>
+          <t>Nhận dư 20.000đ; xác minh hoàn tiền hoặc trừ đơn sau</t>
+        </is>
+      </c>
+      <c r="I59" s="36" t="n"/>
+      <c r="J59" s="36" t="n"/>
+      <c r="K59" s="36" t="n"/>
+      <c r="L59" s="36" t="n"/>
+      <c r="M59" s="36" t="n"/>
+      <c r="N59" s="36" t="n"/>
+      <c r="O59" s="36" t="n"/>
+      <c r="P59" s="39" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>Trả thiếu</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>700000</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Chưa trả</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>1880000</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>1880000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="22" t="inlineStr">
+      <c r="Q59" s="1" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="1" t="n"/>
+      <c r="B60" s="43" t="inlineStr">
         <is>
           <t>Cần kiểm tra</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>800000</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>870000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>TIỀN VỀ THEO GIỜ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Giờ</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Số tiền</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>Giao dịch</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>1020000</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="n">
-        <v>7700000</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="n">
-        <v>350000</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="n">
-        <v>4790000</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="n">
-        <v>2360000</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>VIỆC CẦN LÀM</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Trạng thái</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>Mã đơn</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>Khách hàng</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>SĐT</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>Còn thiếu</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="inlineStr">
-        <is>
-          <t>Việc cần làm</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>Trả thiếu</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>DH1002</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>Trần Thị Bình</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>0902222333</t>
-        </is>
-      </c>
-      <c r="G34" s="19" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H34" s="24" t="inlineStr">
-        <is>
-          <t>Nhắc khách chuyển thêm 500.000đ</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>Chưa trả</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>DH1004</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>Phạm Quốc Dũng</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>0904444555</t>
-        </is>
-      </c>
-      <c r="G35" s="19" t="n">
-        <v>890000</v>
-      </c>
-      <c r="H35" s="24" t="inlineStr">
-        <is>
-          <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>Chưa trả</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="inlineStr">
-        <is>
-          <t>DH1016</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>Mai Phương Thảo</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>0918000111</t>
-        </is>
-      </c>
-      <c r="G36" s="19" t="n">
-        <v>990000</v>
-      </c>
-      <c r="H36" s="24" t="inlineStr">
-        <is>
-          <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="22" t="inlineStr">
-        <is>
-          <t>Cần kiểm tra</t>
-        </is>
-      </c>
-      <c r="C37" s="23" t="inlineStr">
-        <is>
-          <t>DH1006</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>Võ Thanh Em</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>0906666777</t>
-        </is>
-      </c>
-      <c r="G37" s="19" t="n">
-        <v>250000</v>
-      </c>
-      <c r="H37" s="24" t="inlineStr">
-        <is>
-          <t>Mở ảnh z6042817840331_e0d5b8.jpg (chỉ đúng số tiền, chưa đủ để ghép) để xác nhận</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>Cần kiểm tra</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>DH1009</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
-        <is>
-          <t>Bùi Ngọc Lan</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>0909999000</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="24" t="inlineStr">
-        <is>
-          <t>Nhận dư 20.000đ; xác minh hoàn tiền hoặc trừ đơn sau</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>Cần kiểm tra</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>DH1011</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="C60" s="41" t="inlineStr">
         <is>
           <t>Ngô Thị Kim</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>0913444555</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="n">
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="42" t="inlineStr">
+        <is>
+          <t>DH1011 · 0913444555</t>
+        </is>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>Mở ảnh z6042818350288_6ac2e5.jpg (có mã đơn nhưng không đọc được số tiền) để xác nhận</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="n"/>
+      <c r="J60" s="9" t="n"/>
+      <c r="K60" s="9" t="n"/>
+      <c r="L60" s="9" t="n"/>
+      <c r="M60" s="9" t="n"/>
+      <c r="N60" s="9" t="n"/>
+      <c r="O60" s="9" t="n"/>
+      <c r="P60" s="30" t="n">
         <v>620000</v>
       </c>
-      <c r="H39" s="24" t="inlineStr">
-        <is>
-          <t>Mở ảnh z6042818350288_6ac2e5.jpg (có mã đơn nhưng không đọc được số tiền) để xác nhận</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>Ảnh: 17 · ghép tự động 12 (75%) · trùng 1 · cần xem 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>Hóa đơn điện tử: 8 số · khớp 2 · lệch 3 · tải trùng 1 · chỉ có ở một bên 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="25" t="inlineStr">
-        <is>
-          <t>Số tiền lấy từ ảnh khách gửi, chưa phải xác nhận tiền đã vào tài khoản. Xem sao kê trước khi giao đơn lớn. Agent không gửi tin nhắn.</t>
-        </is>
-      </c>
+      <c r="Q60" s="1" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="n"/>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="9" t="n"/>
+      <c r="K61" s="9" t="n"/>
+      <c r="L61" s="9" t="n"/>
+      <c r="M61" s="9" t="n"/>
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="9" t="n"/>
+      <c r="P61" s="9" t="n"/>
+      <c r="Q61" s="1" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n"/>
+      <c r="B62" s="1" t="n"/>
+      <c r="C62" s="1" t="n"/>
+      <c r="D62" s="1" t="n"/>
+      <c r="E62" s="1" t="n"/>
+      <c r="F62" s="1" t="n"/>
+      <c r="G62" s="1" t="n"/>
+      <c r="H62" s="1" t="n"/>
+      <c r="I62" s="1" t="n"/>
+      <c r="J62" s="1" t="n"/>
+      <c r="K62" s="1" t="n"/>
+      <c r="L62" s="1" t="n"/>
+      <c r="M62" s="1" t="n"/>
+      <c r="N62" s="1" t="n"/>
+      <c r="O62" s="1" t="n"/>
+      <c r="P62" s="1" t="n"/>
+      <c r="Q62" s="1" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n"/>
+      <c r="B63" s="44" t="inlineStr">
+        <is>
+          <t>Ảnh: 17 · ghép tự động 12 (75%) · trùng 1 · tạo lúc 09:20 13/10/2026</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n"/>
+      <c r="D63" s="1" t="n"/>
+      <c r="E63" s="1" t="n"/>
+      <c r="F63" s="1" t="n"/>
+      <c r="G63" s="1" t="n"/>
+      <c r="H63" s="1" t="n"/>
+      <c r="I63" s="1" t="n"/>
+      <c r="J63" s="1" t="n"/>
+      <c r="K63" s="1" t="n"/>
+      <c r="L63" s="1" t="n"/>
+      <c r="M63" s="1" t="n"/>
+      <c r="N63" s="1" t="n"/>
+      <c r="O63" s="1" t="n"/>
+      <c r="P63" s="1" t="n"/>
+      <c r="Q63" s="1" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n"/>
+      <c r="B64" s="1" t="n"/>
+      <c r="C64" s="1" t="n"/>
+      <c r="D64" s="1" t="n"/>
+      <c r="E64" s="1" t="n"/>
+      <c r="F64" s="1" t="n"/>
+      <c r="G64" s="1" t="n"/>
+      <c r="H64" s="1" t="n"/>
+      <c r="I64" s="1" t="n"/>
+      <c r="J64" s="1" t="n"/>
+      <c r="K64" s="1" t="n"/>
+      <c r="L64" s="1" t="n"/>
+      <c r="M64" s="1" t="n"/>
+      <c r="N64" s="1" t="n"/>
+      <c r="O64" s="1" t="n"/>
+      <c r="P64" s="1" t="n"/>
+      <c r="Q64" s="1" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n"/>
+      <c r="B65" s="1" t="n"/>
+      <c r="C65" s="1" t="n"/>
+      <c r="D65" s="1" t="n"/>
+      <c r="E65" s="1" t="n"/>
+      <c r="F65" s="1" t="n"/>
+      <c r="G65" s="1" t="n"/>
+      <c r="H65" s="1" t="n"/>
+      <c r="I65" s="1" t="n"/>
+      <c r="J65" s="1" t="n"/>
+      <c r="K65" s="1" t="n"/>
+      <c r="L65" s="1" t="n"/>
+      <c r="M65" s="1" t="n"/>
+      <c r="N65" s="1" t="n"/>
+      <c r="O65" s="1" t="n"/>
+      <c r="P65" s="1" t="n"/>
+      <c r="Q65" s="1" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n"/>
+      <c r="B66" s="1" t="n"/>
+      <c r="C66" s="1" t="n"/>
+      <c r="D66" s="1" t="n"/>
+      <c r="E66" s="1" t="n"/>
+      <c r="F66" s="1" t="n"/>
+      <c r="G66" s="1" t="n"/>
+      <c r="H66" s="1" t="n"/>
+      <c r="I66" s="1" t="n"/>
+      <c r="J66" s="1" t="n"/>
+      <c r="K66" s="1" t="n"/>
+      <c r="L66" s="1" t="n"/>
+      <c r="M66" s="1" t="n"/>
+      <c r="N66" s="1" t="n"/>
+      <c r="O66" s="1" t="n"/>
+      <c r="P66" s="1" t="n"/>
+      <c r="Q66" s="1" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n"/>
+      <c r="B67" s="1" t="n"/>
+      <c r="C67" s="1" t="n"/>
+      <c r="D67" s="1" t="n"/>
+      <c r="E67" s="1" t="n"/>
+      <c r="F67" s="1" t="n"/>
+      <c r="G67" s="1" t="n"/>
+      <c r="H67" s="1" t="n"/>
+      <c r="I67" s="1" t="n"/>
+      <c r="J67" s="1" t="n"/>
+      <c r="K67" s="1" t="n"/>
+      <c r="L67" s="1" t="n"/>
+      <c r="M67" s="1" t="n"/>
+      <c r="N67" s="1" t="n"/>
+      <c r="O67" s="1" t="n"/>
+      <c r="P67" s="1" t="n"/>
+      <c r="Q67" s="1" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n"/>
+      <c r="B68" s="1" t="n"/>
+      <c r="C68" s="1" t="n"/>
+      <c r="D68" s="1" t="n"/>
+      <c r="E68" s="1" t="n"/>
+      <c r="F68" s="1" t="n"/>
+      <c r="G68" s="1" t="n"/>
+      <c r="H68" s="1" t="n"/>
+      <c r="I68" s="1" t="n"/>
+      <c r="J68" s="1" t="n"/>
+      <c r="K68" s="1" t="n"/>
+      <c r="L68" s="1" t="n"/>
+      <c r="M68" s="1" t="n"/>
+      <c r="N68" s="1" t="n"/>
+      <c r="O68" s="1" t="n"/>
+      <c r="P68" s="1" t="n"/>
+      <c r="Q68" s="1" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n"/>
+      <c r="B69" s="1" t="n"/>
+      <c r="C69" s="1" t="n"/>
+      <c r="D69" s="1" t="n"/>
+      <c r="E69" s="1" t="n"/>
+      <c r="F69" s="1" t="n"/>
+      <c r="G69" s="1" t="n"/>
+      <c r="H69" s="1" t="n"/>
+      <c r="I69" s="1" t="n"/>
+      <c r="J69" s="1" t="n"/>
+      <c r="K69" s="1" t="n"/>
+      <c r="L69" s="1" t="n"/>
+      <c r="M69" s="1" t="n"/>
+      <c r="N69" s="1" t="n"/>
+      <c r="O69" s="1" t="n"/>
+      <c r="P69" s="1" t="n"/>
+      <c r="Q69" s="1" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n"/>
+      <c r="B70" s="1" t="n"/>
+      <c r="C70" s="1" t="n"/>
+      <c r="D70" s="1" t="n"/>
+      <c r="E70" s="1" t="n"/>
+      <c r="F70" s="1" t="n"/>
+      <c r="G70" s="1" t="n"/>
+      <c r="H70" s="1" t="n"/>
+      <c r="I70" s="1" t="n"/>
+      <c r="J70" s="1" t="n"/>
+      <c r="K70" s="1" t="n"/>
+      <c r="L70" s="1" t="n"/>
+      <c r="M70" s="1" t="n"/>
+      <c r="N70" s="1" t="n"/>
+      <c r="O70" s="1" t="n"/>
+      <c r="P70" s="1" t="n"/>
+      <c r="Q70" s="1" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n"/>
+      <c r="B71" s="1" t="n"/>
+      <c r="C71" s="1" t="n"/>
+      <c r="D71" s="1" t="n"/>
+      <c r="E71" s="1" t="n"/>
+      <c r="F71" s="1" t="n"/>
+      <c r="G71" s="1" t="n"/>
+      <c r="H71" s="1" t="n"/>
+      <c r="I71" s="1" t="n"/>
+      <c r="J71" s="1" t="n"/>
+      <c r="K71" s="1" t="n"/>
+      <c r="L71" s="1" t="n"/>
+      <c r="M71" s="1" t="n"/>
+      <c r="N71" s="1" t="n"/>
+      <c r="O71" s="1" t="n"/>
+      <c r="P71" s="1" t="n"/>
+      <c r="Q71" s="1" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n"/>
+      <c r="B72" s="1" t="n"/>
+      <c r="C72" s="1" t="n"/>
+      <c r="D72" s="1" t="n"/>
+      <c r="E72" s="1" t="n"/>
+      <c r="F72" s="1" t="n"/>
+      <c r="G72" s="1" t="n"/>
+      <c r="H72" s="1" t="n"/>
+      <c r="I72" s="1" t="n"/>
+      <c r="J72" s="1" t="n"/>
+      <c r="K72" s="1" t="n"/>
+      <c r="L72" s="1" t="n"/>
+      <c r="M72" s="1" t="n"/>
+      <c r="N72" s="1" t="n"/>
+      <c r="O72" s="1" t="n"/>
+      <c r="P72" s="1" t="n"/>
+      <c r="Q72" s="1" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n"/>
+      <c r="B73" s="1" t="n"/>
+      <c r="C73" s="1" t="n"/>
+      <c r="D73" s="1" t="n"/>
+      <c r="E73" s="1" t="n"/>
+      <c r="F73" s="1" t="n"/>
+      <c r="G73" s="1" t="n"/>
+      <c r="H73" s="1" t="n"/>
+      <c r="I73" s="1" t="n"/>
+      <c r="J73" s="1" t="n"/>
+      <c r="K73" s="1" t="n"/>
+      <c r="L73" s="1" t="n"/>
+      <c r="M73" s="1" t="n"/>
+      <c r="N73" s="1" t="n"/>
+      <c r="O73" s="1" t="n"/>
+      <c r="P73" s="1" t="n"/>
+      <c r="Q73" s="1" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n"/>
+      <c r="B74" s="1" t="n"/>
+      <c r="C74" s="1" t="n"/>
+      <c r="D74" s="1" t="n"/>
+      <c r="E74" s="1" t="n"/>
+      <c r="F74" s="1" t="n"/>
+      <c r="G74" s="1" t="n"/>
+      <c r="H74" s="1" t="n"/>
+      <c r="I74" s="1" t="n"/>
+      <c r="J74" s="1" t="n"/>
+      <c r="K74" s="1" t="n"/>
+      <c r="L74" s="1" t="n"/>
+      <c r="M74" s="1" t="n"/>
+      <c r="N74" s="1" t="n"/>
+      <c r="O74" s="1" t="n"/>
+      <c r="P74" s="1" t="n"/>
+      <c r="Q74" s="1" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n"/>
+      <c r="B75" s="1" t="n"/>
+      <c r="C75" s="1" t="n"/>
+      <c r="D75" s="1" t="n"/>
+      <c r="E75" s="1" t="n"/>
+      <c r="F75" s="1" t="n"/>
+      <c r="G75" s="1" t="n"/>
+      <c r="H75" s="1" t="n"/>
+      <c r="I75" s="1" t="n"/>
+      <c r="J75" s="1" t="n"/>
+      <c r="K75" s="1" t="n"/>
+      <c r="L75" s="1" t="n"/>
+      <c r="M75" s="1" t="n"/>
+      <c r="N75" s="1" t="n"/>
+      <c r="O75" s="1" t="n"/>
+      <c r="P75" s="1" t="n"/>
+      <c r="Q75" s="1" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n"/>
+      <c r="B76" s="1" t="n"/>
+      <c r="C76" s="1" t="n"/>
+      <c r="D76" s="1" t="n"/>
+      <c r="E76" s="1" t="n"/>
+      <c r="F76" s="1" t="n"/>
+      <c r="G76" s="1" t="n"/>
+      <c r="H76" s="1" t="n"/>
+      <c r="I76" s="1" t="n"/>
+      <c r="J76" s="1" t="n"/>
+      <c r="K76" s="1" t="n"/>
+      <c r="L76" s="1" t="n"/>
+      <c r="M76" s="1" t="n"/>
+      <c r="N76" s="1" t="n"/>
+      <c r="O76" s="1" t="n"/>
+      <c r="P76" s="1" t="n"/>
+      <c r="Q76" s="1" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n"/>
+      <c r="B77" s="1" t="n"/>
+      <c r="C77" s="1" t="n"/>
+      <c r="D77" s="1" t="n"/>
+      <c r="E77" s="1" t="n"/>
+      <c r="F77" s="1" t="n"/>
+      <c r="G77" s="1" t="n"/>
+      <c r="H77" s="1" t="n"/>
+      <c r="I77" s="1" t="n"/>
+      <c r="J77" s="1" t="n"/>
+      <c r="K77" s="1" t="n"/>
+      <c r="L77" s="1" t="n"/>
+      <c r="M77" s="1" t="n"/>
+      <c r="N77" s="1" t="n"/>
+      <c r="O77" s="1" t="n"/>
+      <c r="P77" s="1" t="n"/>
+      <c r="Q77" s="1" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n"/>
+      <c r="B78" s="1" t="n"/>
+      <c r="C78" s="1" t="n"/>
+      <c r="D78" s="1" t="n"/>
+      <c r="E78" s="1" t="n"/>
+      <c r="F78" s="1" t="n"/>
+      <c r="G78" s="1" t="n"/>
+      <c r="H78" s="1" t="n"/>
+      <c r="I78" s="1" t="n"/>
+      <c r="J78" s="1" t="n"/>
+      <c r="K78" s="1" t="n"/>
+      <c r="L78" s="1" t="n"/>
+      <c r="M78" s="1" t="n"/>
+      <c r="N78" s="1" t="n"/>
+      <c r="O78" s="1" t="n"/>
+      <c r="P78" s="1" t="n"/>
+      <c r="Q78" s="1" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n"/>
+      <c r="B79" s="1" t="n"/>
+      <c r="C79" s="1" t="n"/>
+      <c r="D79" s="1" t="n"/>
+      <c r="E79" s="1" t="n"/>
+      <c r="F79" s="1" t="n"/>
+      <c r="G79" s="1" t="n"/>
+      <c r="H79" s="1" t="n"/>
+      <c r="I79" s="1" t="n"/>
+      <c r="J79" s="1" t="n"/>
+      <c r="K79" s="1" t="n"/>
+      <c r="L79" s="1" t="n"/>
+      <c r="M79" s="1" t="n"/>
+      <c r="N79" s="1" t="n"/>
+      <c r="O79" s="1" t="n"/>
+      <c r="P79" s="1" t="n"/>
+      <c r="Q79" s="1" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n"/>
+      <c r="B80" s="1" t="n"/>
+      <c r="C80" s="1" t="n"/>
+      <c r="D80" s="1" t="n"/>
+      <c r="E80" s="1" t="n"/>
+      <c r="F80" s="1" t="n"/>
+      <c r="G80" s="1" t="n"/>
+      <c r="H80" s="1" t="n"/>
+      <c r="I80" s="1" t="n"/>
+      <c r="J80" s="1" t="n"/>
+      <c r="K80" s="1" t="n"/>
+      <c r="L80" s="1" t="n"/>
+      <c r="M80" s="1" t="n"/>
+      <c r="N80" s="1" t="n"/>
+      <c r="O80" s="1" t="n"/>
+      <c r="P80" s="1" t="n"/>
+      <c r="Q80" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="J6:L7"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="F6:H7"/>
+  <mergeCells count="15">
+    <mergeCell ref="B16:D17"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="N23:P24"/>
+    <mergeCell ref="N19:P20"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N27:P28"/>
+    <mergeCell ref="N31:P32"/>
+    <mergeCell ref="F8:H9"/>
+    <mergeCell ref="J8:L9"/>
+    <mergeCell ref="N8:P9"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="B13:P13"/>
+    <mergeCell ref="B8:D9"/>
+    <mergeCell ref="N30:P30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1549,789 +3090,789 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Mã đơn</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Số điện thoại</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Phải thu</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Đã nhận theo ảnh</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Còn thiếu</t>
         </is>
       </c>
-      <c r="G1" s="26" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="H1" s="45" t="inlineStr">
         <is>
           <t>Ảnh đã ghép</t>
         </is>
       </c>
-      <c r="I1" s="26" t="inlineStr">
+      <c r="I1" s="45" t="inlineStr">
         <is>
           <t>Căn cứ ghép</t>
         </is>
       </c>
-      <c r="J1" s="26" t="inlineStr">
+      <c r="J1" s="45" t="inlineStr">
         <is>
           <t>Việc cần làm</t>
         </is>
       </c>
-      <c r="K1" s="26" t="inlineStr">
+      <c r="K1" s="45" t="inlineStr">
         <is>
           <t>Tin nhắn nhắc (soạn sẵn, chưa gửi)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>DH1001</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="46" t="inlineStr">
         <is>
           <t>Nguyễn Văn An</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="46" t="inlineStr">
         <is>
           <t>0901111222</t>
         </is>
       </c>
-      <c r="D2" s="28" t="n">
+      <c r="D2" s="47" t="n">
         <v>450000</v>
       </c>
-      <c r="E2" s="28" t="n">
+      <c r="E2" s="47" t="n">
         <v>450000</v>
       </c>
-      <c r="F2" s="28" t="n">
+      <c r="F2" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="27" t="inlineStr">
+      <c r="G2" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="48" t="inlineStr">
         <is>
           <t>z6042817353390_8f1c2a.jpg</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="48" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J2" s="29" t="inlineStr">
+      <c r="J2" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
         </is>
       </c>
-      <c r="K2" s="29" t="inlineStr"/>
+      <c r="K2" s="48" t="inlineStr"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>DH1002</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
         <is>
           <t>Trần Thị Bình</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>0902222333</t>
         </is>
       </c>
-      <c r="D3" s="31" t="n">
+      <c r="D3" s="50" t="n">
         <v>1200000</v>
       </c>
-      <c r="E3" s="31" t="n">
+      <c r="E3" s="50" t="n">
         <v>700000</v>
       </c>
-      <c r="F3" s="31" t="n">
+      <c r="F3" s="50" t="n">
         <v>500000</v>
       </c>
-      <c r="G3" s="30" t="inlineStr">
+      <c r="G3" s="49" t="inlineStr">
         <is>
           <t>Trả thiếu</t>
         </is>
       </c>
-      <c r="H3" s="32" t="inlineStr">
+      <c r="H3" s="51" t="inlineStr">
         <is>
           <t>z6042817411205_a7d3e9.jpg</t>
         </is>
       </c>
-      <c r="I3" s="32" t="inlineStr">
+      <c r="I3" s="51" t="inlineStr">
         <is>
           <t>có mã đơn</t>
         </is>
       </c>
-      <c r="J3" s="32" t="inlineStr">
+      <c r="J3" s="51" t="inlineStr">
         <is>
           <t>Nhắc khách chuyển thêm 500.000đ</t>
         </is>
       </c>
-      <c r="K3" s="32" t="inlineStr">
+      <c r="K3" s="51" t="inlineStr">
         <is>
           <t>Chào Trần Thị Bình, shop đã nhận 700.000đ cho đơn DH1002. Đơn còn thiếu 500.000đ, anh/chị kiểm tra giúp shop nhé. Cảm ơn anh/chị!</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>DH1003</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>Lê Minh Châu</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>0912345678</t>
         </is>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="47" t="n">
         <v>320000</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="47" t="n">
         <v>320000</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="27" t="inlineStr">
+      <c r="G4" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>z6042817502117_3b9e01.jpg</t>
         </is>
       </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="I4" s="48" t="inlineStr">
         <is>
           <t>có số điện thoại, đúng số tiền</t>
         </is>
       </c>
-      <c r="J4" s="29" t="inlineStr">
+      <c r="J4" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
         </is>
       </c>
-      <c r="K4" s="29" t="inlineStr"/>
+      <c r="K4" s="48" t="inlineStr"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>DH1004</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>Phạm Quốc Dũng</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>0904444555</t>
         </is>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="53" t="n">
         <v>890000</v>
       </c>
-      <c r="E5" s="34" t="n">
+      <c r="E5" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="53" t="n">
         <v>890000</v>
       </c>
-      <c r="G5" s="33" t="inlineStr">
+      <c r="G5" s="52" t="inlineStr">
         <is>
           <t>Chưa trả</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr"/>
-      <c r="I5" s="35" t="inlineStr"/>
-      <c r="J5" s="35" t="inlineStr">
+      <c r="H5" s="54" t="inlineStr"/>
+      <c r="I5" s="54" t="inlineStr"/>
+      <c r="J5" s="54" t="inlineStr">
         <is>
           <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
         </is>
       </c>
-      <c r="K5" s="35" t="inlineStr">
+      <c r="K5" s="54" t="inlineStr">
         <is>
           <t>Chào Phạm Quốc Dũng, với đơn DH1004 (890.000đ), shop chưa ghép được ảnh thanh toán trong dữ liệu cuối ngày. Nếu anh/chị đã chuyển, gửi giúp shop ảnh chuyển khoản nhé. Cảm ơn anh/chị!</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>DH1005</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>Hoàng Thu Hà</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>0905555666</t>
         </is>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="47" t="n">
         <v>560000</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="47" t="n">
         <v>560000</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="27" t="inlineStr">
+      <c r="G6" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H6" s="29" t="inlineStr">
+      <c r="H6" s="48" t="inlineStr">
         <is>
           <t>z6042817618842_c41f77.jpg, z6042817733015_77ab02.jpg</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="48" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="J6" s="29" t="inlineStr">
+      <c r="J6" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
         </is>
       </c>
-      <c r="K6" s="29" t="inlineStr"/>
+      <c r="K6" s="48" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>DH1006</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>Võ Thanh Em</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>0906666777</t>
         </is>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="56" t="n">
         <v>250000</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="56" t="n">
         <v>250000</v>
       </c>
-      <c r="G7" s="36" t="inlineStr">
+      <c r="G7" s="55" t="inlineStr">
         <is>
           <t>Cần kiểm tra</t>
         </is>
       </c>
-      <c r="H7" s="38" t="inlineStr"/>
-      <c r="I7" s="38" t="inlineStr"/>
-      <c r="J7" s="38" t="inlineStr">
+      <c r="H7" s="57" t="inlineStr"/>
+      <c r="I7" s="57" t="inlineStr"/>
+      <c r="J7" s="57" t="inlineStr">
         <is>
           <t>Mở ảnh z6042817840331_e0d5b8.jpg (chỉ đúng số tiền, chưa đủ để ghép) để xác nhận</t>
         </is>
       </c>
-      <c r="K7" s="38" t="inlineStr"/>
+      <c r="K7" s="57" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>DH1007</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>Đỗ Gia Huy</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>0907777888</t>
         </is>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="47" t="n">
         <v>1500000</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="47" t="n">
         <v>1500000</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H8" s="29" t="inlineStr">
+      <c r="H8" s="48" t="inlineStr">
         <is>
           <t>z6042817921456_19ce4d.jpg</t>
         </is>
       </c>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="48" t="inlineStr">
         <is>
           <t>có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J8" s="29" t="inlineStr">
+      <c r="J8" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
         </is>
       </c>
-      <c r="K8" s="29" t="inlineStr"/>
+      <c r="K8" s="48" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>DH1008</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Công ty TNHH Nội thất Gỗ Việt</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>0243888999</t>
         </is>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="47" t="n">
         <v>5400000</v>
       </c>
-      <c r="E9" s="28" t="n">
+      <c r="E9" s="47" t="n">
         <v>5400000</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="27" t="inlineStr">
+      <c r="G9" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H9" s="29" t="inlineStr">
+      <c r="H9" s="48" t="inlineStr">
         <is>
           <t>z6042818034470_5d2a90.png</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="I9" s="48" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J9" s="29" t="inlineStr">
+      <c r="J9" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; xem sao kê trước khi xác nhận đơn hoặc giao hàng</t>
         </is>
       </c>
-      <c r="K9" s="29" t="inlineStr"/>
+      <c r="K9" s="48" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>DH1009</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>Bùi Ngọc Lan</t>
         </is>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C10" s="55" t="inlineStr">
         <is>
           <t>0909999000</t>
         </is>
       </c>
-      <c r="D10" s="37" t="n">
+      <c r="D10" s="56" t="n">
         <v>780000</v>
       </c>
-      <c r="E10" s="37" t="n">
+      <c r="E10" s="56" t="n">
         <v>800000</v>
       </c>
-      <c r="F10" s="37" t="n">
+      <c r="F10" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="36" t="inlineStr">
+      <c r="G10" s="55" t="inlineStr">
         <is>
           <t>Cần kiểm tra</t>
         </is>
       </c>
-      <c r="H10" s="38" t="inlineStr">
+      <c r="H10" s="57" t="inlineStr">
         <is>
           <t>z6042818115902_b8e6c3.jpg</t>
         </is>
       </c>
-      <c r="I10" s="38" t="inlineStr">
+      <c r="I10" s="57" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="J10" s="38" t="inlineStr">
+      <c r="J10" s="57" t="inlineStr">
         <is>
           <t>Nhận dư 20.000đ; xác minh hoàn tiền hoặc trừ đơn sau</t>
         </is>
       </c>
-      <c r="K10" s="38" t="inlineStr"/>
+      <c r="K10" s="57" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>DH1010</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>Đặng Hữu Phước</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>0911222333</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="47" t="n">
         <v>350000</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="47" t="n">
         <v>350000</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H11" s="29" t="inlineStr">
+      <c r="H11" s="48" t="inlineStr">
         <is>
           <t>z6042818207719_0f4ad1.jpg</t>
         </is>
       </c>
-      <c r="I11" s="29" t="inlineStr">
+      <c r="I11" s="48" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J11" s="29" t="inlineStr">
+      <c r="J11" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
         </is>
       </c>
-      <c r="K11" s="29" t="inlineStr"/>
+      <c r="K11" s="48" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>DH1011</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>Ngô Thị Kim</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="55" t="inlineStr">
         <is>
           <t>0913444555</t>
         </is>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="56" t="n">
         <v>620000</v>
       </c>
-      <c r="E12" s="37" t="n">
+      <c r="E12" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="37" t="n">
+      <c r="F12" s="56" t="n">
         <v>620000</v>
       </c>
-      <c r="G12" s="36" t="inlineStr">
+      <c r="G12" s="55" t="inlineStr">
         <is>
           <t>Cần kiểm tra</t>
         </is>
       </c>
-      <c r="H12" s="38" t="inlineStr"/>
-      <c r="I12" s="38" t="inlineStr"/>
-      <c r="J12" s="38" t="inlineStr">
+      <c r="H12" s="57" t="inlineStr"/>
+      <c r="I12" s="57" t="inlineStr"/>
+      <c r="J12" s="57" t="inlineStr">
         <is>
           <t>Mở ảnh z6042818350288_6ac2e5.jpg (có mã đơn nhưng không đọc được số tiền) để xác nhận</t>
         </is>
       </c>
-      <c r="K12" s="38" t="inlineStr"/>
+      <c r="K12" s="57" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>DH1012</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>Công ty CP Sự kiện Ánh Dương</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>0283777666</t>
         </is>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="47" t="n">
         <v>3240000</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="47" t="n">
         <v>3240000</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="27" t="inlineStr">
+      <c r="G13" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="H13" s="48" t="inlineStr">
         <is>
           <t>z6042818462531_2e7b9f.png</t>
         </is>
       </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="I13" s="48" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J13" s="29" t="inlineStr">
+      <c r="J13" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; xem sao kê trước khi xác nhận đơn hoặc giao hàng</t>
         </is>
       </c>
-      <c r="K13" s="29" t="inlineStr"/>
+      <c r="K13" s="48" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>DH1013</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>Trịnh Văn Long</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>0915666777</t>
         </is>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="47" t="n">
         <v>1150000</v>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="47" t="n">
         <v>1150000</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="27" t="inlineStr">
+      <c r="G14" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H14" s="48" t="inlineStr">
         <is>
           <t>z6042818573004_d9f310.jpg</t>
         </is>
       </c>
-      <c r="I14" s="29" t="inlineStr">
+      <c r="I14" s="48" t="inlineStr">
         <is>
           <t>1 lần chuyển cho 2 đơn: có mã các đơn, tổng tiền khớp</t>
         </is>
       </c>
-      <c r="J14" s="29" t="inlineStr">
+      <c r="J14" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
         </is>
       </c>
-      <c r="K14" s="29" t="inlineStr"/>
+      <c r="K14" s="48" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>DH1014</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>Trịnh Văn Long</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>0915666777</t>
         </is>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="47" t="n">
         <v>400000</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="47" t="n">
         <v>400000</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="27" t="inlineStr">
+      <c r="G15" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H15" s="29" t="inlineStr">
+      <c r="H15" s="48" t="inlineStr">
         <is>
           <t>z6042818573004_d9f310.jpg</t>
         </is>
       </c>
-      <c r="I15" s="29" t="inlineStr">
+      <c r="I15" s="48" t="inlineStr">
         <is>
           <t>1 lần chuyển cho 2 đơn: có mã các đơn, tổng tiền khớp</t>
         </is>
       </c>
-      <c r="J15" s="29" t="inlineStr">
+      <c r="J15" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; kiểm tra sao kê theo quy trình trước khi xác nhận đơn</t>
         </is>
       </c>
-      <c r="K15" s="29" t="inlineStr"/>
+      <c r="K15" s="48" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t>DH1015</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Lý Thanh Tâm</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>0917888999</t>
         </is>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="47" t="n">
         <v>2100000</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="47" t="n">
         <v>2100000</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="27" t="inlineStr">
+      <c r="G16" s="46" t="inlineStr">
         <is>
           <t>Đã trả đủ</t>
         </is>
       </c>
-      <c r="H16" s="29" t="inlineStr">
+      <c r="H16" s="48" t="inlineStr">
         <is>
           <t>z6042818680147_41b8ac.jpg</t>
         </is>
       </c>
-      <c r="I16" s="29" t="inlineStr">
+      <c r="I16" s="48" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="J16" s="29" t="inlineStr">
+      <c r="J16" s="48" t="inlineStr">
         <is>
           <t>Đủ theo ảnh; xem sao kê trước khi xác nhận đơn hoặc giao hàng</t>
         </is>
       </c>
-      <c r="K16" s="29" t="inlineStr"/>
+      <c r="K16" s="48" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>DH1016</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>Mai Phương Thảo</t>
         </is>
       </c>
-      <c r="C17" s="33" t="inlineStr">
+      <c r="C17" s="52" t="inlineStr">
         <is>
           <t>0918000111</t>
         </is>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D17" s="53" t="n">
         <v>990000</v>
       </c>
-      <c r="E17" s="34" t="n">
+      <c r="E17" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="53" t="n">
         <v>990000</v>
       </c>
-      <c r="G17" s="33" t="inlineStr">
+      <c r="G17" s="52" t="inlineStr">
         <is>
           <t>Chưa trả</t>
         </is>
       </c>
-      <c r="H17" s="35" t="inlineStr"/>
-      <c r="I17" s="35" t="inlineStr"/>
-      <c r="J17" s="35" t="inlineStr">
+      <c r="H17" s="54" t="inlineStr"/>
+      <c r="I17" s="54" t="inlineStr"/>
+      <c r="J17" s="54" t="inlineStr">
         <is>
           <t>Chưa tìm thấy ảnh ghép chắc; kiểm tra Zalo/sao kê trước khi nhắc khách</t>
         </is>
       </c>
-      <c r="K17" s="35" t="inlineStr">
+      <c r="K17" s="54" t="inlineStr">
         <is>
           <t>Chào Mai Phương Thảo, với đơn DH1016 (990.000đ), shop chưa ghép được ảnh thanh toán trong dữ liệu cuối ngày. Nếu anh/chị đã chuyển, gửi giúp shop ảnh chuyển khoản nhé. Cảm ơn anh/chị!</t>
         </is>
@@ -2365,102 +3906,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Tệp ảnh</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Số tiền đọc được</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Nội dung</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Người chuyển</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Mã giao dịch</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Thời gian</t>
         </is>
       </c>
-      <c r="G1" s="26" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Ghép vào đơn</t>
         </is>
       </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="H1" s="45" t="inlineStr">
         <is>
           <t>Căn cứ</t>
         </is>
       </c>
-      <c r="I1" s="26" t="inlineStr">
+      <c r="I1" s="45" t="inlineStr">
         <is>
           <t>Kết quả</t>
         </is>
       </c>
-      <c r="J1" s="26" t="inlineStr">
+      <c r="J1" s="45" t="inlineStr">
         <is>
           <t>Chữ đọc được trên ảnh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>z6042817353390_8f1c2a.jpg</t>
         </is>
       </c>
-      <c r="B2" s="40" t="n">
+      <c r="B2" s="59" t="n">
         <v>450000</v>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="58" t="inlineStr">
         <is>
           <t>DH1001 NGUYEN VAN AN</t>
         </is>
       </c>
-      <c r="D2" s="39" t="inlineStr">
+      <c r="D2" s="58" t="inlineStr">
         <is>
           <t>NGUYEN VAN AN</t>
         </is>
       </c>
-      <c r="E2" s="39" t="inlineStr">
+      <c r="E2" s="58" t="inlineStr">
         <is>
           <t>FT26285104411</t>
         </is>
       </c>
-      <c r="F2" s="39" t="inlineStr">
+      <c r="F2" s="58" t="inlineStr">
         <is>
           <t>12/10/2026 08:41:07</t>
         </is>
       </c>
-      <c r="G2" s="39" t="inlineStr">
+      <c r="G2" s="58" t="inlineStr">
         <is>
           <t>DH1001</t>
         </is>
       </c>
-      <c r="H2" s="39" t="inlineStr">
+      <c r="H2" s="58" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I2" s="39" t="inlineStr">
+      <c r="I2" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J2" s="39" t="inlineStr">
+      <c r="J2" s="58" t="inlineStr">
         <is>
           <t>08:41 al RKM
 Sen Vàng Bank
@@ -2477,46 +4018,46 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>z6042817411205_a7d3e9.jpg</t>
         </is>
       </c>
-      <c r="B3" s="40" t="n">
+      <c r="B3" s="59" t="n">
         <v>700000</v>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="58" t="inlineStr">
         <is>
           <t>DH1002 chuyen truoc</t>
         </is>
       </c>
-      <c r="D3" s="39" t="n"/>
-      <c r="E3" s="39" t="inlineStr">
+      <c r="D3" s="58" t="n"/>
+      <c r="E3" s="58" t="inlineStr">
         <is>
           <t>FT26285219034</t>
         </is>
       </c>
-      <c r="F3" s="39" t="inlineStr">
+      <c r="F3" s="58" t="inlineStr">
         <is>
           <t>12/10/2026 09:12:45</t>
         </is>
       </c>
-      <c r="G3" s="39" t="inlineStr">
+      <c r="G3" s="58" t="inlineStr">
         <is>
           <t>DH1002</t>
         </is>
       </c>
-      <c r="H3" s="39" t="inlineStr">
+      <c r="H3" s="58" t="inlineStr">
         <is>
           <t>có mã đơn</t>
         </is>
       </c>
-      <c r="I3" s="39" t="inlineStr">
+      <c r="I3" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J3" s="39" t="inlineStr">
+      <c r="J3" s="58" t="inlineStr">
         <is>
           <t>09:12 | o_o
 Bién Xanh Bank
@@ -2534,46 +4075,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>z6042817502117_3b9e01.jpg</t>
         </is>
       </c>
-      <c r="B4" s="40" t="n">
+      <c r="B4" s="59" t="n">
         <v>320000</v>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="58" t="inlineStr">
         <is>
           <t>0912345678 thanh toan</t>
         </is>
       </c>
-      <c r="D4" s="39" t="n"/>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="D4" s="58" t="n"/>
+      <c r="E4" s="58" t="inlineStr">
         <is>
           <t>MM2610120933</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="58" t="inlineStr">
         <is>
           <t>09:33 - 12/10/2026</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" s="58" t="inlineStr">
         <is>
           <t>DH1003</t>
         </is>
       </c>
-      <c r="H4" s="39" t="inlineStr">
+      <c r="H4" s="58" t="inlineStr">
         <is>
           <t>có số điện thoại, đúng số tiền</t>
         </is>
       </c>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="I4" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="J4" s="58" t="inlineStr">
         <is>
           <t>09:33
 "' ï
@@ -2594,50 +4135,50 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t>z6042817618842_c41f77.jpg</t>
         </is>
       </c>
-      <c r="B5" s="40" t="n">
+      <c r="B5" s="59" t="n">
         <v>300000</v>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="58" t="inlineStr">
         <is>
           <t>DH1005 lan 1</t>
         </is>
       </c>
-      <c r="D5" s="39" t="inlineStr">
+      <c r="D5" s="58" t="inlineStr">
         <is>
           <t>HOANG THU HA</t>
         </is>
       </c>
-      <c r="E5" s="39" t="inlineStr">
+      <c r="E5" s="58" t="inlineStr">
         <is>
           <t>DT26101200871</t>
         </is>
       </c>
-      <c r="F5" s="39" t="inlineStr">
+      <c r="F5" s="58" t="inlineStr">
         <is>
           <t>12/10/2026 10:02:19</t>
         </is>
       </c>
-      <c r="G5" s="39" t="inlineStr">
+      <c r="G5" s="58" t="inlineStr">
         <is>
           <t>DH1005</t>
         </is>
       </c>
-      <c r="H5" s="39" t="inlineStr">
+      <c r="H5" s="58" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="I5" s="39" t="inlineStr">
+      <c r="I5" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J5" s="39" t="inlineStr">
+      <c r="J5" s="58" t="inlineStr">
         <is>
           <t>10:02
 aul
@@ -2657,50 +4198,50 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>z6042817733015_77ab02.jpg</t>
         </is>
       </c>
-      <c r="B6" s="40" t="n">
+      <c r="B6" s="59" t="n">
         <v>260000</v>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>DH1005 lan 2</t>
         </is>
       </c>
-      <c r="D6" s="39" t="inlineStr">
+      <c r="D6" s="58" t="inlineStr">
         <is>
           <t>HOANG THU HA</t>
         </is>
       </c>
-      <c r="E6" s="39" t="inlineStr">
+      <c r="E6" s="58" t="inlineStr">
         <is>
           <t>FT26285310927</t>
         </is>
       </c>
-      <c r="F6" s="39" t="inlineStr">
+      <c r="F6" s="58" t="inlineStr">
         <is>
           <t>12/10/2026 15:47:52</t>
         </is>
       </c>
-      <c r="G6" s="39" t="inlineStr">
+      <c r="G6" s="58" t="inlineStr">
         <is>
           <t>DH1005</t>
         </is>
       </c>
-      <c r="H6" s="39" t="inlineStr">
+      <c r="H6" s="58" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="I6" s="39" t="inlineStr">
+      <c r="I6" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J6" s="39" t="inlineStr">
+      <c r="J6" s="58" t="inlineStr">
         <is>
           <t>15:47 a l
 Sen Vàng Bank
@@ -2717,46 +4258,46 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>z6042817840331_e0d5b8.jpg</t>
         </is>
       </c>
-      <c r="B7" s="42" t="n">
+      <c r="B7" s="61" t="n">
         <v>250000</v>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>chuyen tien</t>
         </is>
       </c>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="inlineStr">
+      <c r="D7" s="60" t="n"/>
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>FT26285322108</t>
         </is>
       </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="F7" s="60" t="inlineStr">
         <is>
           <t>12/10/2026 10:50:31</t>
         </is>
       </c>
-      <c r="G7" s="41" t="inlineStr">
+      <c r="G7" s="60" t="inlineStr">
         <is>
           <t>DH1006</t>
         </is>
       </c>
-      <c r="H7" s="41" t="inlineStr">
+      <c r="H7" s="60" t="inlineStr">
         <is>
           <t>Chỉ đúng số tiền, chưa đủ để ghép</t>
         </is>
       </c>
-      <c r="I7" s="41" t="inlineStr">
+      <c r="I7" s="60" t="inlineStr">
         <is>
           <t>Gợi ý, cần người xác nhận</t>
         </is>
       </c>
-      <c r="J7" s="41" t="inlineStr">
+      <c r="J7" s="60" t="inlineStr">
         <is>
           <t>40:50 "Am l
 Biên Xanh Bank
@@ -2774,50 +4315,50 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>z6042817921456_19ce4d.jpg</t>
         </is>
       </c>
-      <c r="B8" s="40" t="n">
+      <c r="B8" s="59" t="n">
         <v>1500000</v>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="58" t="inlineStr">
         <is>
           <t>DO GIA HUY thanh toan</t>
         </is>
       </c>
-      <c r="D8" s="39" t="inlineStr">
+      <c r="D8" s="58" t="inlineStr">
         <is>
           <t>DO GIA HUY</t>
         </is>
       </c>
-      <c r="E8" s="39" t="inlineStr">
+      <c r="E8" s="58" t="inlineStr">
         <is>
           <t>DT26101201544</t>
         </is>
       </c>
-      <c r="F8" s="39" t="inlineStr">
+      <c r="F8" s="58" t="inlineStr">
         <is>
           <t>12/10/2026 11:05:44</t>
         </is>
       </c>
-      <c r="G8" s="39" t="inlineStr">
+      <c r="G8" s="58" t="inlineStr">
         <is>
           <t>DH1007</t>
         </is>
       </c>
-      <c r="H8" s="39" t="inlineStr">
+      <c r="H8" s="58" t="inlineStr">
         <is>
           <t>có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I8" s="39" t="inlineStr">
+      <c r="I8" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J8" s="39" t="inlineStr">
+      <c r="J8" s="58" t="inlineStr">
         <is>
           <t>11:05
 aul
@@ -2837,42 +4378,42 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="58" t="inlineStr">
         <is>
           <t>z6042818034470_5d2a90.png</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="59" t="n">
         <v>5400000</v>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="58" t="inlineStr">
         <is>
           <t>DH1008 TT HD 00000126</t>
         </is>
       </c>
-      <c r="D9" s="39" t="n"/>
-      <c r="E9" s="39" t="n"/>
-      <c r="F9" s="39" t="inlineStr">
+      <c r="D9" s="58" t="n"/>
+      <c r="E9" s="58" t="n"/>
+      <c r="F9" s="58" t="inlineStr">
         <is>
           <t>12/10/2026 11:31:02</t>
         </is>
       </c>
-      <c r="G9" s="39" t="inlineStr">
+      <c r="G9" s="58" t="inlineStr">
         <is>
           <t>DH1008</t>
         </is>
       </c>
-      <c r="H9" s="39" t="inlineStr">
+      <c r="H9" s="58" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I9" s="39" t="inlineStr">
+      <c r="I9" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J9" s="39" t="inlineStr">
+      <c r="J9" s="58" t="inlineStr">
         <is>
           <t>Kết quả giao dịch: Chuyên khoản thành công
 1903 2222 1111
@@ -2896,38 +4437,38 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>z6042818115902_b8e6c3.jpg</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="59" t="n">
         <v>800000</v>
       </c>
-      <c r="C10" s="39" t="n"/>
-      <c r="D10" s="39" t="n"/>
-      <c r="E10" s="39" t="n"/>
-      <c r="F10" s="39" t="inlineStr">
+      <c r="C10" s="58" t="n"/>
+      <c r="D10" s="58" t="n"/>
+      <c r="E10" s="58" t="n"/>
+      <c r="F10" s="58" t="inlineStr">
         <is>
           <t>11:42 - 12/10/2026</t>
         </is>
       </c>
-      <c r="G10" s="39" t="inlineStr">
+      <c r="G10" s="58" t="inlineStr">
         <is>
           <t>DH1009</t>
         </is>
       </c>
-      <c r="H10" s="39" t="inlineStr">
+      <c r="H10" s="58" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="I10" s="39" t="inlineStr">
+      <c r="I10" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J10" s="39" t="inlineStr">
+      <c r="J10" s="58" t="inlineStr">
         <is>
           <t>11:42
 "' ï
@@ -2948,46 +4489,46 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="58" t="inlineStr">
         <is>
           <t>z6042818207719_0f4ad1.jpg</t>
         </is>
       </c>
-      <c r="B11" s="40" t="n">
+      <c r="B11" s="59" t="n">
         <v>350000</v>
       </c>
-      <c r="C11" s="39" t="n"/>
-      <c r="D11" s="39" t="inlineStr">
+      <c r="C11" s="58" t="n"/>
+      <c r="D11" s="58" t="inlineStr">
         <is>
           <t>DANG HUU PHUOC</t>
         </is>
       </c>
-      <c r="E11" s="39" t="inlineStr">
+      <c r="E11" s="58" t="inlineStr">
         <is>
           <t>FT26285512870</t>
         </is>
       </c>
-      <c r="F11" s="39" t="inlineStr">
+      <c r="F11" s="58" t="inlineStr">
         <is>
           <t>42/10/2026 13:22:16</t>
         </is>
       </c>
-      <c r="G11" s="39" t="inlineStr">
+      <c r="G11" s="58" t="inlineStr">
         <is>
           <t>DH1010</t>
         </is>
       </c>
-      <c r="H11" s="39" t="inlineStr">
+      <c r="H11" s="58" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I11" s="39" t="inlineStr">
+      <c r="I11" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J11" s="39" t="inlineStr">
+      <c r="J11" s="58" t="inlineStr">
         <is>
           <t>13:22 wt a)
 Sen Vang Bank
@@ -3004,48 +4545,48 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="62" t="inlineStr">
         <is>
           <t>z6042818350288_6ac2e5.jpg</t>
         </is>
       </c>
-      <c r="B12" s="44" t="n"/>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="B12" s="63" t="n"/>
+      <c r="C12" s="62" t="inlineStr">
         <is>
           <t>DH1011 Ngo Thi Kim</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
+      <c r="D12" s="62" t="inlineStr">
         <is>
           <t>NGO THI KIM</t>
         </is>
       </c>
-      <c r="E12" s="43" t="inlineStr">
+      <c r="E12" s="62" t="inlineStr">
         <is>
           <t>DT26101202230</t>
         </is>
       </c>
-      <c r="F12" s="43" t="inlineStr">
+      <c r="F12" s="62" t="inlineStr">
         <is>
           <t>12/10/2026 14:01:33</t>
         </is>
       </c>
-      <c r="G12" s="43" t="inlineStr">
+      <c r="G12" s="62" t="inlineStr">
         <is>
           <t>DH1011</t>
         </is>
       </c>
-      <c r="H12" s="43" t="inlineStr">
+      <c r="H12" s="62" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách</t>
         </is>
       </c>
-      <c r="I12" s="43" t="inlineStr">
+      <c r="I12" s="62" t="inlineStr">
         <is>
           <t>Không đọc được số tiền; mở ảnh kiểm tra</t>
         </is>
       </c>
-      <c r="J12" s="43" t="inlineStr">
+      <c r="J12" s="62" t="inlineStr">
         <is>
           <t>Người chuyển: NGO THI KIM
 Từ tài khoản: 2201 8899 7766
@@ -3059,46 +4600,46 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>z6042818462531_2e7b9f.png</t>
         </is>
       </c>
-      <c r="B13" s="40" t="n">
+      <c r="B13" s="59" t="n">
         <v>3240000</v>
       </c>
-      <c r="C13" s="39" t="inlineStr">
+      <c r="C13" s="58" t="inlineStr">
         <is>
           <t>DH1012 thanh toan hoa don 00000127</t>
         </is>
       </c>
-      <c r="D13" s="39" t="n"/>
-      <c r="E13" s="39" t="inlineStr">
+      <c r="D13" s="58" t="n"/>
+      <c r="E13" s="58" t="inlineStr">
         <is>
           <t>FT26285618833</t>
         </is>
       </c>
-      <c r="F13" s="39" t="inlineStr">
+      <c r="F13" s="58" t="inlineStr">
         <is>
           <t>12/40/2026 14:20:09</t>
         </is>
       </c>
-      <c r="G13" s="39" t="inlineStr">
+      <c r="G13" s="58" t="inlineStr">
         <is>
           <t>DH1012</t>
         </is>
       </c>
-      <c r="H13" s="39" t="inlineStr">
+      <c r="H13" s="58" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I13" s="39" t="inlineStr">
+      <c r="I13" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J13" s="39" t="inlineStr">
+      <c r="J13" s="58" t="inlineStr">
         <is>
           <t>Kết quả giao dịch: Chuyên khoản thành công
 1903 2222 1111
@@ -3122,46 +4663,46 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>z6042818573004_d9f310.jpg</t>
         </is>
       </c>
-      <c r="B14" s="40" t="n">
+      <c r="B14" s="59" t="n">
         <v>1550000</v>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" s="58" t="inlineStr">
         <is>
           <t>DH1013 DH1014</t>
         </is>
       </c>
-      <c r="D14" s="39" t="n"/>
-      <c r="E14" s="39" t="inlineStr">
+      <c r="D14" s="58" t="n"/>
+      <c r="E14" s="58" t="inlineStr">
         <is>
           <t>FT26285702264</t>
         </is>
       </c>
-      <c r="F14" s="39" t="inlineStr">
+      <c r="F14" s="58" t="inlineStr">
         <is>
           <t>12/10/2026 14:48:55</t>
         </is>
       </c>
-      <c r="G14" s="39" t="inlineStr">
+      <c r="G14" s="58" t="inlineStr">
         <is>
           <t>DH1013, DH1014</t>
         </is>
       </c>
-      <c r="H14" s="39" t="inlineStr">
+      <c r="H14" s="58" t="inlineStr">
         <is>
           <t>1 lần chuyển cho 2 đơn: có mã các đơn, tổng tiền khớp</t>
         </is>
       </c>
-      <c r="I14" s="39" t="inlineStr">
+      <c r="I14" s="58" t="inlineStr">
         <is>
           <t>Đã ghép, chia cho 2 đơn</t>
         </is>
       </c>
-      <c r="J14" s="39" t="inlineStr">
+      <c r="J14" s="58" t="inlineStr">
         <is>
           <t>14:48 || o_o
 Bién Xanh Bank
@@ -3179,46 +4720,46 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>z6042818680147_41b8ac.jpg</t>
         </is>
       </c>
-      <c r="B15" s="40" t="n">
+      <c r="B15" s="59" t="n">
         <v>2100000</v>
       </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="C15" s="58" t="inlineStr">
         <is>
           <t>DH1015 Ly Thanh Tam</t>
         </is>
       </c>
-      <c r="D15" s="39" t="n"/>
-      <c r="E15" s="39" t="inlineStr">
+      <c r="D15" s="58" t="n"/>
+      <c r="E15" s="58" t="inlineStr">
         <is>
           <t>MM2610121537</t>
         </is>
       </c>
-      <c r="F15" s="39" t="inlineStr">
+      <c r="F15" s="58" t="inlineStr">
         <is>
           <t>15:37 - 12/10/2026</t>
         </is>
       </c>
-      <c r="G15" s="39" t="inlineStr">
+      <c r="G15" s="58" t="inlineStr">
         <is>
           <t>DH1015</t>
         </is>
       </c>
-      <c r="H15" s="39" t="inlineStr">
+      <c r="H15" s="58" t="inlineStr">
         <is>
           <t>có mã đơn, có tên khách, đúng số tiền</t>
         </is>
       </c>
-      <c r="I15" s="39" t="inlineStr">
+      <c r="I15" s="58" t="inlineStr">
         <is>
           <t>Đã ghép</t>
         </is>
       </c>
-      <c r="J15" s="39" t="inlineStr">
+      <c r="J15" s="58" t="inlineStr">
         <is>
           <t>15:37
 "' ï
@@ -3239,46 +4780,46 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>z6042818791260_a3c6d2.jpg</t>
         </is>
       </c>
-      <c r="B16" s="42" t="n">
+      <c r="B16" s="61" t="n">
         <v>430000</v>
       </c>
-      <c r="C16" s="41" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>DH0987 Phan Van Quang</t>
         </is>
       </c>
-      <c r="D16" s="41" t="inlineStr">
+      <c r="D16" s="60" t="inlineStr">
         <is>
           <t>PHAN VAN QUANG</t>
         </is>
       </c>
-      <c r="E16" s="41" t="inlineStr">
+      <c r="E16" s="60" t="inlineStr">
         <is>
           <t>FT26285800412</t>
         </is>
       </c>
-      <c r="F16" s="41" t="inlineStr">
+      <c r="F16" s="60" t="inlineStr">
         <is>
           <t>12/10/2026 16:12:40</t>
         </is>
       </c>
-      <c r="G16" s="41" t="n"/>
-      <c r="H16" s="41" t="inlineStr">
+      <c r="G16" s="60" t="n"/>
+      <c r="H16" s="60" t="inlineStr">
         <is>
           <t>Không thấy mã đơn, SĐT, tên khách hay số tiền nào khớp</t>
         </is>
       </c>
-      <c r="I16" s="41" t="inlineStr">
+      <c r="I16" s="60" t="inlineStr">
         <is>
           <t>Chưa ghép được; xem ảnh và tìm đơn</t>
         </is>
       </c>
-      <c r="J16" s="41" t="inlineStr">
+      <c r="J16" s="60" t="inlineStr">
         <is>
           <t>46:12 | MHỊ
 Sen Vàng Bank
@@ -3295,42 +4836,42 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t>z6042819002388_3b9e01.jpg</t>
         </is>
       </c>
-      <c r="B17" s="44" t="n">
+      <c r="B17" s="63" t="n">
         <v>320000</v>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t>0912345678 thanh toan</t>
         </is>
       </c>
-      <c r="D17" s="43" t="n"/>
-      <c r="E17" s="43" t="inlineStr">
+      <c r="D17" s="62" t="n"/>
+      <c r="E17" s="62" t="inlineStr">
         <is>
           <t>MM2610120933</t>
         </is>
       </c>
-      <c r="F17" s="43" t="inlineStr">
+      <c r="F17" s="62" t="inlineStr">
         <is>
           <t>09:33 - 12/10/2026</t>
         </is>
       </c>
-      <c r="G17" s="43" t="n"/>
-      <c r="H17" s="43" t="inlineStr">
+      <c r="G17" s="62" t="n"/>
+      <c r="H17" s="62" t="inlineStr">
         <is>
           <t>có số điện thoại, đúng số tiền</t>
         </is>
       </c>
-      <c r="I17" s="43" t="inlineStr">
+      <c r="I17" s="62" t="inlineStr">
         <is>
           <t>Trùng với ảnh z6042817502117_3b9e01.jpg; không cộng tiền</t>
         </is>
       </c>
-      <c r="J17" s="43" t="inlineStr">
+      <c r="J17" s="62" t="inlineStr">
         <is>
           <t>09:33
 "' ï
@@ -3351,28 +4892,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="62" t="inlineStr">
         <is>
           <t>z6042819115630_7e21aa.jpg</t>
         </is>
       </c>
-      <c r="B18" s="44" t="n"/>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="43" t="n"/>
-      <c r="E18" s="43" t="n"/>
-      <c r="F18" s="43" t="n"/>
-      <c r="G18" s="43" t="n"/>
-      <c r="H18" s="43" t="inlineStr">
+      <c r="B18" s="63" t="n"/>
+      <c r="C18" s="62" t="n"/>
+      <c r="D18" s="62" t="n"/>
+      <c r="E18" s="62" t="n"/>
+      <c r="F18" s="62" t="n"/>
+      <c r="G18" s="62" t="n"/>
+      <c r="H18" s="62" t="inlineStr">
         <is>
           <t>Không thấy mã đơn, SĐT, tên khách hay số tiền nào khớp</t>
         </is>
       </c>
-      <c r="I18" s="43" t="inlineStr">
+      <c r="I18" s="62" t="inlineStr">
         <is>
           <t>Không đọc được số tiền; có thể không phải biên nhận</t>
         </is>
       </c>
-      <c r="J18" s="43" t="inlineStr">
+      <c r="J18" s="62" t="inlineStr">
         <is>
           <t>Mau bó hoa số 3 —- còn hàng không shop?</t>
         </is>
@@ -3382,4 +4923,230 @@
   <autoFilter ref="A1:J18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Giờ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tiền về</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cộng dồn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>450000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1020000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1470000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1770000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11h</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7700000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9470000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9470000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9820000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4790000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14610000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2360000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16970000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16970000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>16970000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>16970000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Giá trị đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Đã trả đủ</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>15470000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Trả thiếu</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chưa trả</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1880000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cần kiểm tra</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1650000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>